--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -509,7 +509,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-15 17:01 UK time. Scanning days with history: 1 (2026-10-15 to 2026-10-15)</t>
+          <t>Generated 2026-10-15 21:28 UK time. Scanning days with history: 1 (2026-10-15 to 2026-10-15)</t>
         </is>
       </c>
     </row>

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -509,7 +509,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-15 21:28 UK time. Scanning days with history: 1 (2026-10-15 to 2026-10-15)</t>
+          <t>Generated 2026-10-15 21:39 UK time. Scanning days with history: 1 (2026-10-15 to 2026-10-15)</t>
         </is>
       </c>
     </row>

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -101,10 +101,10 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -509,7 +509,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-15 21:39 UK time. Scanning days with history: 1 (2026-10-15 to 2026-10-15)</t>
+          <t>Generated 2026-10-16 21:08 UK time. Scanning days with history: 1 (2026-10-15 to 2026-10-15)</t>
         </is>
       </c>
     </row>
@@ -668,23 +668,47 @@
         <v>2</v>
       </c>
       <c r="C9" s="6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E9" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="8" t="n"/>
-      <c r="I9" s="8" t="n"/>
-      <c r="J9" s="8" t="n"/>
-      <c r="K9" s="8" t="n"/>
-      <c r="L9" s="8" t="n"/>
-      <c r="M9" s="8" t="n"/>
-      <c r="N9" s="8" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G9" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I9" s="8" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="J9" s="8" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="K9" s="6" t="n"/>
+      <c r="L9" s="6" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="M9" s="6" t="n">
+        <v>-1.19</v>
+      </c>
+      <c r="N9" s="6" t="inlineStr">
+        <is>
+          <t>30%</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
@@ -704,15 +728,15 @@
       <c r="E10" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="8" t="n"/>
-      <c r="I10" s="8" t="n"/>
-      <c r="J10" s="8" t="n"/>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="8" t="n"/>
-      <c r="M10" s="8" t="n"/>
-      <c r="N10" s="8" t="n"/>
+      <c r="F10" s="9" t="n"/>
+      <c r="G10" s="9" t="n"/>
+      <c r="H10" s="9" t="n"/>
+      <c r="I10" s="9" t="n"/>
+      <c r="J10" s="9" t="n"/>
+      <c r="K10" s="9" t="n"/>
+      <c r="L10" s="9" t="n"/>
+      <c r="M10" s="9" t="n"/>
+      <c r="N10" s="9" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -747,10 +771,10 @@
           <t>50%</t>
         </is>
       </c>
-      <c r="I11" s="9" t="n">
+      <c r="I11" s="8" t="n">
         <v>-0.305</v>
       </c>
-      <c r="J11" s="9" t="n">
+      <c r="J11" s="8" t="n">
         <v>-0.9360000000000001</v>
       </c>
       <c r="K11" s="6" t="n">
@@ -778,23 +802,49 @@
         <v>2</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D12" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E12" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="8" t="n"/>
-      <c r="I12" s="8" t="n"/>
-      <c r="J12" s="8" t="n"/>
-      <c r="K12" s="8" t="n"/>
-      <c r="L12" s="8" t="n"/>
-      <c r="M12" s="8" t="n"/>
-      <c r="N12" s="8" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G12" s="6" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="I12" s="8" t="n">
+        <v>-1.221</v>
+      </c>
+      <c r="J12" s="8" t="n">
+        <v>-1.853</v>
+      </c>
+      <c r="K12" s="6" t="n">
+        <v>0.061</v>
+      </c>
+      <c r="L12" s="6" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="M12" s="6" t="n">
+        <v>-2.44</v>
+      </c>
+      <c r="N12" s="6" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="5" t="inlineStr">
@@ -814,15 +864,15 @@
       <c r="E13" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="8" t="n"/>
-      <c r="I13" s="8" t="n"/>
-      <c r="J13" s="8" t="n"/>
-      <c r="K13" s="8" t="n"/>
-      <c r="L13" s="8" t="n"/>
-      <c r="M13" s="8" t="n"/>
-      <c r="N13" s="8" t="n"/>
+      <c r="F13" s="9" t="n"/>
+      <c r="G13" s="9" t="n"/>
+      <c r="H13" s="9" t="n"/>
+      <c r="I13" s="9" t="n"/>
+      <c r="J13" s="9" t="n"/>
+      <c r="K13" s="9" t="n"/>
+      <c r="L13" s="9" t="n"/>
+      <c r="M13" s="9" t="n"/>
+      <c r="N13" s="9" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -888,23 +938,49 @@
         <v>2</v>
       </c>
       <c r="C15" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="8" t="n"/>
-      <c r="I15" s="8" t="n"/>
-      <c r="J15" s="8" t="n"/>
-      <c r="K15" s="8" t="n"/>
-      <c r="L15" s="8" t="n"/>
-      <c r="M15" s="8" t="n"/>
-      <c r="N15" s="8" t="n"/>
+        <v>0</v>
+      </c>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="G15" s="6" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H15" s="6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="I15" s="7" t="n">
+        <v>4.419</v>
+      </c>
+      <c r="J15" s="7" t="n">
+        <v>4.419</v>
+      </c>
+      <c r="K15" s="6" t="n">
+        <v>3.561</v>
+      </c>
+      <c r="L15" s="6" t="n">
+        <v>8.84</v>
+      </c>
+      <c r="M15" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="6" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
@@ -924,15 +1000,15 @@
       <c r="E16" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="8" t="n"/>
-      <c r="I16" s="8" t="n"/>
-      <c r="J16" s="8" t="n"/>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="8" t="n"/>
-      <c r="M16" s="8" t="n"/>
-      <c r="N16" s="8" t="n"/>
+      <c r="F16" s="9" t="n"/>
+      <c r="G16" s="9" t="n"/>
+      <c r="H16" s="9" t="n"/>
+      <c r="I16" s="9" t="n"/>
+      <c r="J16" s="9" t="n"/>
+      <c r="K16" s="9" t="n"/>
+      <c r="L16" s="9" t="n"/>
+      <c r="M16" s="9" t="n"/>
+      <c r="N16" s="9" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -967,10 +1043,10 @@
           <t>24%</t>
         </is>
       </c>
-      <c r="I17" s="9" t="n">
+      <c r="I17" s="8" t="n">
         <v>-0.451</v>
       </c>
-      <c r="J17" s="9" t="n">
+      <c r="J17" s="8" t="n">
         <v>-0.956</v>
       </c>
       <c r="K17" s="6" t="n">
@@ -998,23 +1074,49 @@
         <v>2</v>
       </c>
       <c r="C18" s="6" t="n">
+        <v>97</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E18" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="D18" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="6" t="n">
-        <v>100</v>
-      </c>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="8" t="n"/>
-      <c r="I18" s="8" t="n"/>
-      <c r="J18" s="8" t="n"/>
-      <c r="K18" s="8" t="n"/>
-      <c r="L18" s="8" t="n"/>
-      <c r="M18" s="8" t="n"/>
-      <c r="N18" s="8" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>19%</t>
+        </is>
+      </c>
+      <c r="G18" s="6" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="H18" s="6" t="inlineStr">
+        <is>
+          <t>9%</t>
+        </is>
+      </c>
+      <c r="I18" s="8" t="n">
+        <v>-0.431</v>
+      </c>
+      <c r="J18" s="8" t="n">
+        <v>-0.9360000000000001</v>
+      </c>
+      <c r="K18" s="6" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="L18" s="6" t="n">
+        <v>-41.82</v>
+      </c>
+      <c r="M18" s="6" t="n">
+        <v>-43.34</v>
+      </c>
+      <c r="N18" s="6" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -1034,15 +1136,15 @@
       <c r="E19" s="6" t="n">
         <v>100</v>
       </c>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="8" t="n"/>
-      <c r="I19" s="8" t="n"/>
-      <c r="J19" s="8" t="n"/>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="8" t="n"/>
-      <c r="M19" s="8" t="n"/>
-      <c r="N19" s="8" t="n"/>
+      <c r="F19" s="9" t="n"/>
+      <c r="G19" s="9" t="n"/>
+      <c r="H19" s="9" t="n"/>
+      <c r="I19" s="9" t="n"/>
+      <c r="J19" s="9" t="n"/>
+      <c r="K19" s="9" t="n"/>
+      <c r="L19" s="9" t="n"/>
+      <c r="M19" s="9" t="n"/>
+      <c r="N19" s="9" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1">
       <c r="A21" s="10" t="inlineStr">
@@ -1297,7 +1399,7 @@
       <c r="F8" s="6" t="n">
         <v>-0.286</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="8" t="n">
         <v>-0.602</v>
       </c>
       <c r="H8" s="6" t="inlineStr">
@@ -1418,7 +1520,7 @@
       <c r="F13" s="6" t="n">
         <v>-0.228</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="8" t="n">
         <v>-0.451</v>
       </c>
       <c r="H13" s="6" t="inlineStr">
@@ -1503,7 +1605,7 @@
       <c r="F17" s="6" t="n">
         <v>-0.266</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="8" t="n">
         <v>-0.397</v>
       </c>
       <c r="H17" s="6" t="inlineStr">
@@ -1539,7 +1641,7 @@
       <c r="F18" s="6" t="n">
         <v>-0.21</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="8" t="n">
         <v>-0.475</v>
       </c>
       <c r="H18" s="6" t="inlineStr">
@@ -1624,7 +1726,7 @@
       <c r="F22" s="6" t="n">
         <v>-0.07000000000000001</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="8" t="n">
         <v>-0.298</v>
       </c>
       <c r="H22" s="6" t="inlineStr">
@@ -1660,7 +1762,7 @@
       <c r="F23" s="6" t="n">
         <v>-0.353</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="8" t="n">
         <v>-0.574</v>
       </c>
       <c r="H23" s="6" t="inlineStr">
@@ -1781,7 +1883,7 @@
       <c r="F28" s="6" t="n">
         <v>-0.249</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="8" t="n">
         <v>-0.485</v>
       </c>
       <c r="H28" s="6" t="inlineStr">
@@ -1866,7 +1968,7 @@
       <c r="F32" s="6" t="n">
         <v>-0.104</v>
       </c>
-      <c r="G32" s="9" t="n">
+      <c r="G32" s="8" t="n">
         <v>-0.267</v>
       </c>
       <c r="H32" s="6" t="inlineStr">
@@ -2529,10 +2631,12 @@
       </c>
       <c r="O2" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P2" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P2" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q2" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -2603,10 +2707,12 @@
       </c>
       <c r="O3" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P3" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P3" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q3" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -2677,10 +2783,12 @@
       </c>
       <c r="O4" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P4" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P4" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q4" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -2751,10 +2859,12 @@
       </c>
       <c r="O5" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P5" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P5" s="5" t="n">
+        <v>3.64</v>
+      </c>
       <c r="Q5" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -2825,10 +2935,12 @@
       </c>
       <c r="O6" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P6" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P6" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q6" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -2899,10 +3011,12 @@
       </c>
       <c r="O7" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P7" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P7" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q7" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -2973,10 +3087,12 @@
       </c>
       <c r="O8" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P8" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P8" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q8" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -3047,10 +3163,12 @@
       </c>
       <c r="O9" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P9" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P9" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q9" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -3121,10 +3239,12 @@
       </c>
       <c r="O10" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P10" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P10" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q10" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -3193,7 +3313,7 @@
       <c r="N11" s="5" t="n"/>
       <c r="O11" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="P11" s="5" t="n"/>
@@ -3267,10 +3387,12 @@
       </c>
       <c r="O12" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P12" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P12" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q12" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -3341,10 +3463,12 @@
       </c>
       <c r="O13" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P13" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P13" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q13" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -3415,10 +3539,12 @@
       </c>
       <c r="O14" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P14" s="5" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="P14" s="5" t="n">
+        <v>0.426</v>
+      </c>
       <c r="Q14" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -3489,10 +3615,12 @@
       </c>
       <c r="O15" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P15" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P15" s="5" t="n">
+        <v>3.067</v>
+      </c>
       <c r="Q15" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -3563,10 +3691,12 @@
       </c>
       <c r="O16" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P16" s="5" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="P16" s="5" t="n">
+        <v>0.824</v>
+      </c>
       <c r="Q16" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -3637,10 +3767,12 @@
       </c>
       <c r="O17" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P17" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P17" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q17" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -3711,10 +3843,12 @@
       </c>
       <c r="O18" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P18" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P18" s="5" t="n">
+        <v>-4</v>
+      </c>
       <c r="Q18" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -3785,10 +3919,12 @@
       </c>
       <c r="O19" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P19" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P19" s="5" t="n">
+        <v>1.742</v>
+      </c>
       <c r="Q19" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -3859,10 +3995,12 @@
       </c>
       <c r="O20" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P20" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P20" s="5" t="n">
+        <v>-1.25</v>
+      </c>
       <c r="Q20" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -3933,10 +4071,12 @@
       </c>
       <c r="O21" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P21" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P21" s="5" t="n">
+        <v>3.139</v>
+      </c>
       <c r="Q21" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -4007,10 +4147,12 @@
       </c>
       <c r="O22" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P22" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P22" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q22" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -4081,10 +4223,12 @@
       </c>
       <c r="O23" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P23" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P23" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q23" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -4155,10 +4299,12 @@
       </c>
       <c r="O24" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P24" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P24" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q24" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -4229,10 +4375,12 @@
       </c>
       <c r="O25" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P25" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P25" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q25" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -4303,10 +4451,12 @@
       </c>
       <c r="O26" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P26" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P26" s="5" t="n">
+        <v>-1.016</v>
+      </c>
       <c r="Q26" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -4377,10 +4527,12 @@
       </c>
       <c r="O27" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P27" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P27" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q27" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -4451,10 +4603,12 @@
       </c>
       <c r="O28" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P28" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P28" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="Q28" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -4525,10 +4679,12 @@
       </c>
       <c r="O29" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P29" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P29" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q29" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -4599,10 +4755,12 @@
       </c>
       <c r="O30" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P30" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P30" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q30" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -4673,10 +4831,12 @@
       </c>
       <c r="O31" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P31" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P31" s="5" t="n">
+        <v>1.774</v>
+      </c>
       <c r="Q31" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -4747,10 +4907,12 @@
       </c>
       <c r="O32" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P32" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P32" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q32" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -4819,7 +4981,7 @@
       <c r="N33" s="5" t="n"/>
       <c r="O33" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="P33" s="5" t="n"/>
@@ -4893,10 +5055,12 @@
       </c>
       <c r="O34" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P34" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P34" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q34" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -4967,10 +5131,12 @@
       </c>
       <c r="O35" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P35" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P35" s="5" t="n">
+        <v>1.4</v>
+      </c>
       <c r="Q35" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -5041,10 +5207,12 @@
       </c>
       <c r="O36" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P36" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P36" s="5" t="n">
+        <v>1.82</v>
+      </c>
       <c r="Q36" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -5115,10 +5283,12 @@
       </c>
       <c r="O37" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P37" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P37" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q37" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -5189,10 +5359,12 @@
       </c>
       <c r="O38" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P38" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P38" s="5" t="n">
+        <v>3</v>
+      </c>
       <c r="Q38" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -5263,10 +5435,12 @@
       </c>
       <c r="O39" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P39" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P39" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q39" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -5337,10 +5511,12 @@
       </c>
       <c r="O40" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P40" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P40" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q40" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -5411,10 +5587,12 @@
       </c>
       <c r="O41" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P41" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P41" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q41" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -5485,10 +5663,12 @@
       </c>
       <c r="O42" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P42" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P42" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q42" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -5559,10 +5739,12 @@
       </c>
       <c r="O43" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P43" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P43" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q43" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -5633,10 +5815,12 @@
       </c>
       <c r="O44" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P44" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P44" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q44" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -5707,10 +5891,12 @@
       </c>
       <c r="O45" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P45" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P45" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q45" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -5781,10 +5967,12 @@
       </c>
       <c r="O46" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P46" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P46" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q46" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -5855,10 +6043,12 @@
       </c>
       <c r="O47" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P47" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P47" s="5" t="n">
+        <v>2.586</v>
+      </c>
       <c r="Q47" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -5929,10 +6119,12 @@
       </c>
       <c r="O48" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P48" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P48" s="5" t="n">
+        <v>1.507</v>
+      </c>
       <c r="Q48" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -6003,10 +6195,12 @@
       </c>
       <c r="O49" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P49" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P49" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q49" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -6077,10 +6271,12 @@
       </c>
       <c r="O50" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P50" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P50" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q50" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -6151,10 +6347,12 @@
       </c>
       <c r="O51" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P51" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P51" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q51" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -6225,10 +6423,12 @@
       </c>
       <c r="O52" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P52" s="5" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="P52" s="5" t="n">
+        <v>0.8169999999999999</v>
+      </c>
       <c r="Q52" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -6299,10 +6499,12 @@
       </c>
       <c r="O53" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P53" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P53" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q53" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -6373,10 +6575,12 @@
       </c>
       <c r="O54" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P54" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P54" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q54" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -6447,10 +6651,12 @@
       </c>
       <c r="O55" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P55" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P55" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q55" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -6519,7 +6725,7 @@
       <c r="N56" s="5" t="n"/>
       <c r="O56" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>skipped</t>
         </is>
       </c>
       <c r="P56" s="5" t="n"/>
@@ -6593,10 +6799,12 @@
       </c>
       <c r="O57" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P57" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P57" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q57" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -6667,10 +6875,12 @@
       </c>
       <c r="O58" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P58" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P58" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q58" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -6741,10 +6951,12 @@
       </c>
       <c r="O59" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P59" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P59" s="5" t="n">
+        <v>-1.05</v>
+      </c>
       <c r="Q59" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -6815,10 +7027,12 @@
       </c>
       <c r="O60" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P60" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P60" s="5" t="n">
+        <v>4.808</v>
+      </c>
       <c r="Q60" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -6889,10 +7103,12 @@
       </c>
       <c r="O61" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P61" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P61" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q61" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -6963,10 +7179,12 @@
       </c>
       <c r="O62" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P62" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P62" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q62" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -7037,10 +7255,12 @@
       </c>
       <c r="O63" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P63" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P63" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q63" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -7111,10 +7331,12 @@
       </c>
       <c r="O64" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P64" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P64" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q64" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -7185,10 +7407,12 @@
       </c>
       <c r="O65" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P65" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P65" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q65" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -7259,10 +7483,12 @@
       </c>
       <c r="O66" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P66" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P66" s="5" t="n">
+        <v>2.125</v>
+      </c>
       <c r="Q66" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -7333,10 +7559,12 @@
       </c>
       <c r="O67" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P67" s="5" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="P67" s="5" t="n">
+        <v>1.558</v>
+      </c>
       <c r="Q67" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -7407,10 +7635,12 @@
       </c>
       <c r="O68" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P68" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P68" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q68" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -7481,10 +7711,12 @@
       </c>
       <c r="O69" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P69" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P69" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q69" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -7555,10 +7787,12 @@
       </c>
       <c r="O70" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P70" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P70" s="5" t="n">
+        <v>-1.193</v>
+      </c>
       <c r="Q70" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -7629,10 +7863,12 @@
       </c>
       <c r="O71" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P71" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P71" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q71" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -7703,10 +7939,12 @@
       </c>
       <c r="O72" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P72" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P72" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q72" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -7777,10 +8015,12 @@
       </c>
       <c r="O73" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P73" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P73" s="5" t="n">
+        <v>0.866</v>
+      </c>
       <c r="Q73" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -7851,10 +8091,12 @@
       </c>
       <c r="O74" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P74" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P74" s="5" t="n">
+        <v>3.946</v>
+      </c>
       <c r="Q74" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -7925,10 +8167,12 @@
       </c>
       <c r="O75" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P75" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P75" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q75" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -7999,10 +8243,12 @@
       </c>
       <c r="O76" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P76" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P76" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q76" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -8073,10 +8319,12 @@
       </c>
       <c r="O77" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P77" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P77" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q77" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -8147,10 +8395,12 @@
       </c>
       <c r="O78" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P78" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P78" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q78" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -8221,10 +8471,12 @@
       </c>
       <c r="O79" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P79" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P79" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q79" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -8295,10 +8547,12 @@
       </c>
       <c r="O80" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P80" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P80" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q80" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -8369,10 +8623,12 @@
       </c>
       <c r="O81" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P81" s="5" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="P81" s="5" t="n">
+        <v>2.876</v>
+      </c>
       <c r="Q81" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -8443,10 +8699,12 @@
       </c>
       <c r="O82" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P82" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P82" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q82" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -8517,10 +8775,12 @@
       </c>
       <c r="O83" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P83" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P83" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q83" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -8591,10 +8851,12 @@
       </c>
       <c r="O84" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P84" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P84" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q84" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -8665,10 +8927,12 @@
       </c>
       <c r="O85" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P85" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P85" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q85" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -8739,10 +9003,12 @@
       </c>
       <c r="O86" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P86" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P86" s="5" t="n">
+        <v>2.086</v>
+      </c>
       <c r="Q86" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -8813,10 +9079,12 @@
       </c>
       <c r="O87" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P87" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P87" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q87" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -8887,10 +9155,12 @@
       </c>
       <c r="O88" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P88" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P88" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q88" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -8961,10 +9231,12 @@
       </c>
       <c r="O89" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P89" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P89" s="5" t="n">
+        <v>-1.553</v>
+      </c>
       <c r="Q89" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -9035,10 +9307,12 @@
       </c>
       <c r="O90" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P90" s="5" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="P90" s="5" t="n">
+        <v>1.399</v>
+      </c>
       <c r="Q90" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -9109,10 +9383,12 @@
       </c>
       <c r="O91" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P91" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P91" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q91" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -9183,10 +9459,12 @@
       </c>
       <c r="O92" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P92" s="5" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="P92" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q92" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -9257,10 +9535,12 @@
       </c>
       <c r="O93" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P93" s="5" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="P93" s="5" t="n">
+        <v>0.843</v>
+      </c>
       <c r="Q93" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -9331,10 +9611,12 @@
       </c>
       <c r="O94" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P94" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P94" s="5" t="n">
+        <v>2.855</v>
+      </c>
       <c r="Q94" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -9405,10 +9687,12 @@
       </c>
       <c r="O95" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P95" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P95" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q95" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -9479,10 +9763,12 @@
       </c>
       <c r="O96" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P96" s="5" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="P96" s="5" t="n">
+        <v>1.582</v>
+      </c>
       <c r="Q96" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -9553,10 +9839,12 @@
       </c>
       <c r="O97" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P97" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P97" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q97" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -9627,10 +9915,12 @@
       </c>
       <c r="O98" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P98" s="5" t="n"/>
+          <t>target</t>
+        </is>
+      </c>
+      <c r="P98" s="5" t="n">
+        <v>0.257</v>
+      </c>
       <c r="Q98" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -9701,10 +9991,12 @@
       </c>
       <c r="O99" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P99" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P99" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q99" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -9775,10 +10067,12 @@
       </c>
       <c r="O100" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P100" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P100" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q100" s="5" t="inlineStr">
         <is>
           <t>pending</t>
@@ -9849,10 +10143,12 @@
       </c>
       <c r="O101" s="5" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P101" s="5" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="P101" s="5" t="n">
+        <v>-1</v>
+      </c>
       <c r="Q101" s="5" t="inlineStr">
         <is>
           <t>pending</t>

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -509,7 +509,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-16 21:08 UK time. Scanning days with history: 1 (2026-10-15 to 2026-10-15)</t>
+          <t>Generated 2026-10-16 21:16 UK time. Scanning days with history: 1 (2026-10-15 to 2026-10-15)</t>
         </is>
       </c>
     </row>

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -509,7 +509,7 @@
     <row r="2" ht="15" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-16 21:16 UK time. Scanning days with history: 1 (2026-10-15 to 2026-10-15)</t>
+          <t>Generated 2026-10-16 21:31 UK time. Scanning days with history: 1 (2026-10-15 to 2026-10-15)</t>
         </is>
       </c>
     </row>

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -763,7 +763,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-21 17:06 UK time. Corrected simulation: availability-session-v2. Research only; no real orders.</t>
+          <t>Generated 2026-10-21 20:05 UK time. Corrected simulation: availability-session-v2. Research only; no real orders.</t>
         </is>
       </c>
     </row>
@@ -1013,10 +1013,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Each scenario below is a different way of choosing which ideas to trade from the same scans. All figures are pounds per £100 trade after dealing costs, plus stamp duty on buys. Every scenario uses the same entry, exit and cost rules, so they can be compared fairly.</t>
+          <t>The scanner finds many ideas each day. Each scenario below is a different rule for choosing which of those ideas to trade, so you can see which rule works best. Every scenario uses the same ideas, the same entry price (the next 15-minute candle's open), the same stop and target, and the same costs, so the only difference is the choosing rule. Figures are pounds per £100 trade, after 10p dealing and 50p stamp duty on buys.</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>What it does</t>
+          <t>What it does, in plain English</t>
         </is>
       </c>
     </row>
@@ -1041,7 +1041,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>At 10:30 each day, takes the single highest-scoring idea from the first scan available at or after that time.</t>
+          <t>Once a day at 10:30, take the scanner's single best-scoring idea. One trade a day, always at 10:30. Question it answers: is the scanner's number 1 idea better than an average idea?</t>
         </is>
       </c>
     </row>
@@ -1053,11 +1053,11 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>The same, but takes the two highest-scoring ideas (one per share). This is the main mock trader shown on the Summary and Mock Trades sheets.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="30" customHeight="1">
+          <t>Once a day at 10:30, take the two best-scoring ideas (two different shares). Two trades a day. This is the 'Mock Trades' sheet.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="45" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Top 2 per day, persistent</t>
@@ -1065,7 +1065,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Like Top 2, but only ideas that had already shown up in at least two scans that morning, i.e. the setup had held its shape rather than appearing once. Tests whether waiting for confirmation helps.</t>
+          <t>Like Top 2, but an idea only counts if the scanner had also flagged it in an earlier scan that morning. Example: Burberry flagged at 10:00 and still flagged at 10:30 qualifies; an idea seen for the first time at 10:30 does not. Up to two trades a day, sometimes none. Question: do ideas that have lasted a while do better than brand-new ones?</t>
         </is>
       </c>
     </row>
@@ -1077,7 +1077,7 @@
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Enters ideas as they trigger during the day, best score first within a scan, up to 3 a day and one per share. Shown trade by trade on the Live Mock Trades sheet.</t>
+          <t>No fixed time: takes ideas as each scan finds them, from the 10:00 scan onwards, until it has 3 for the day (never two on the same share). This is the 'Live Mock Trades' sheet.</t>
         </is>
       </c>
     </row>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Every idea the scanner flagged, entered once at the first time it appeared that day. This is the benchmark: it is what picking ideas at random would earn. If a strategy can't beat the pool, its way of choosing adds nothing.</t>
+          <t>Every idea the scanner found, as if you had traded all of them (each idea once a day). This is the yardstick: a choosing rule is only useful if its average beats this one.</t>
         </is>
       </c>
     </row>
@@ -1097,14 +1097,14 @@
     <row r="11" ht="60" customHeight="1">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Columns: Selected = ideas the scenario chose. Completed = trades with a final result. Pending = hold period not finished yet. Missing data = prices unavailable, so left out rather than counted as a loss. Skipped = never entered because the price had already passed the stop or target. Avg net per trade = average profit or loss per trade after all fees. Difference vs pool = how much better (+) or worse (-) than the random-pick benchmark.</t>
+          <t>How to read the tables: Selected = trades the rule chose. Completed = trades with a final result. Pending = not finished yet. Missing data = Yahoo's prices had a gap, so the result can't be worked out (left out, not counted as a loss). Skipped = never entered because the price had already jumped past the stop or target. Avg net per trade = average profit or loss per £100 after costs. Difference vs pool = how much better (+) or worse (-) than trading every idea.</t>
         </is>
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Hold periods: each section repeats the comparison allowing trades to stay open for up to 1, 2 or 5 trading days before closing at the price at that time. They are alternatives, not extra trades: don't add sections together.</t>
+          <t>How much to trust it: with fewer than about 100 completed trades in a row, differences between scenarios are mostly luck. The three tables are the same comparison with trades allowed to stay open for up to 1, 2 or 5 trading days; they are alternatives, so don't add them together.</t>
         </is>
       </c>
     </row>
@@ -2522,10 +2522,10 @@
     </row>
     <row r="63"/>
     <row r="64"/>
-    <row r="65" ht="30" customHeight="1">
+    <row r="65" ht="45" customHeight="1">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>There is no fixed break-even target-hit rate: fills, gaps, target payoffs, timeouts and fees vary. Worst fall from peak uses realised results in exit order and excludes open-position valuation. Completed price events do not establish profitability.</t>
+          <t>Target / Stop / Timeout = how trades ended: reached the target, hit the stop, or were still open at the end of the holding time and closed at the last price. Profitable / Losing count trades after costs, so a trade can reach its target and still lose if the move was smaller than the costs. Worst fall from peak = the biggest drop in running profit, adding trades up in the order they closed.</t>
         </is>
       </c>
     </row>

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -763,7 +763,7 @@
     <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-21 20:05 UK time. Corrected simulation: availability-session-v2. Research only; no real orders.</t>
+          <t>Generated 2026-10-21 22:38 UK time. Corrected simulation: availability-session-v2. Research only; no real orders.</t>
         </is>
       </c>
     </row>
@@ -1193,10 +1193,10 @@
         <v>-0.27</v>
       </c>
       <c r="H16" s="5" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="I16" s="5" t="n">
-        <v>0.19</v>
+        <v>0.18</v>
       </c>
       <c r="J16" s="6" t="inlineStr">
         <is>
@@ -1229,10 +1229,10 @@
         <v>-0.19</v>
       </c>
       <c r="H17" s="5" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="I17" s="5" t="n">
-        <v>0.27</v>
+        <v>0.26</v>
       </c>
       <c r="J17" s="6" t="inlineStr">
         <is>
@@ -1265,10 +1265,10 @@
         <v>0.32</v>
       </c>
       <c r="H18" s="5" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="I18" s="5" t="n">
-        <v>0.78</v>
+        <v>0.77</v>
       </c>
       <c r="J18" s="6" t="inlineStr">
         <is>
@@ -1301,10 +1301,10 @@
         <v>-0.49</v>
       </c>
       <c r="H19" s="5" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="I19" s="5" t="n">
-        <v>-0.03</v>
+        <v>-0.04</v>
       </c>
       <c r="J19" s="6" t="inlineStr">
         <is>
@@ -1322,10 +1322,10 @@
         <v>456</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="D20" s="6" t="n">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="E20" s="6" t="n">
         <v>0</v>
@@ -1334,10 +1334,10 @@
         <v>25</v>
       </c>
       <c r="G20" s="5" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="H20" s="5" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="I20" s="5" t="n">
         <v>0</v>
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="B28" s="6" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C28" s="6" t="n">
         <v>43</v>
@@ -1560,22 +1560,22 @@
         <v>224</v>
       </c>
       <c r="E28" s="6" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
       <c r="F28" s="6" t="n">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="G28" s="6" t="n">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H28" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I28" s="5" t="n">
-        <v>-154.12</v>
+        <v>-152.94</v>
       </c>
       <c r="J28" s="5" t="n">
-        <v>-157.16</v>
+        <v>-155.98</v>
       </c>
     </row>
     <row r="29"/>
@@ -1664,10 +1664,10 @@
         <v>-0.67</v>
       </c>
       <c r="H33" s="5" t="n">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
       <c r="I33" s="5" t="n">
-        <v>-0.16</v>
+        <v>-0.18</v>
       </c>
       <c r="J33" s="6" t="inlineStr">
         <is>
@@ -1700,10 +1700,10 @@
         <v>-0.31</v>
       </c>
       <c r="H34" s="5" t="n">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
       <c r="I34" s="5" t="n">
-        <v>0.2</v>
+        <v>0.18</v>
       </c>
       <c r="J34" s="6" t="inlineStr">
         <is>
@@ -1736,10 +1736,10 @@
         <v>0.3</v>
       </c>
       <c r="H35" s="5" t="n">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
       <c r="I35" s="5" t="n">
-        <v>0.8</v>
+        <v>0.78</v>
       </c>
       <c r="J35" s="6" t="inlineStr">
         <is>
@@ -1772,10 +1772,10 @@
         <v>-0.92</v>
       </c>
       <c r="H36" s="5" t="n">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
       <c r="I36" s="5" t="n">
-        <v>-0.42</v>
+        <v>-0.44</v>
       </c>
       <c r="J36" s="6" t="inlineStr">
         <is>
@@ -1793,10 +1793,10 @@
         <v>456</v>
       </c>
       <c r="C37" s="6" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D37" s="6" t="n">
-        <v>113</v>
+        <v>110</v>
       </c>
       <c r="E37" s="6" t="n">
         <v>0</v>
@@ -1805,10 +1805,10 @@
         <v>25</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>-0.5</v>
+        <v>-0.49</v>
       </c>
       <c r="I37" s="5" t="n">
         <v>0</v>
@@ -2022,7 +2022,7 @@
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="C45" s="6" t="n">
         <v>64</v>
@@ -2031,22 +2031,22 @@
         <v>248</v>
       </c>
       <c r="E45" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F45" s="6" t="n">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="G45" s="6" t="n">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H45" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I45" s="5" t="n">
-        <v>-160.13</v>
+        <v>-156.7</v>
       </c>
       <c r="J45" s="5" t="n">
-        <v>-161.25</v>
+        <v>-160.12</v>
       </c>
     </row>
     <row r="46"/>
@@ -2135,10 +2135,10 @@
         <v>-0.67</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="I50" s="5" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="J50" s="6" t="inlineStr">
         <is>
@@ -2171,10 +2171,10 @@
         <v>-0.31</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="I51" s="5" t="n">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="J51" s="6" t="inlineStr">
         <is>
@@ -2207,7 +2207,7 @@
         <v>0.3</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="I52" s="5" t="n">
         <v>0.82</v>
@@ -2243,7 +2243,7 @@
         <v>-0.92</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="I53" s="5" t="n">
         <v>-0.4</v>
@@ -2264,10 +2264,10 @@
         <v>456</v>
       </c>
       <c r="C54" s="6" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="D54" s="6" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="E54" s="6" t="n">
         <v>0</v>
@@ -2276,10 +2276,10 @@
         <v>25</v>
       </c>
       <c r="G54" s="5" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="H54" s="5" t="n">
-        <v>-0.52</v>
+        <v>-0.53</v>
       </c>
       <c r="I54" s="5" t="n">
         <v>0</v>
@@ -2493,13 +2493,13 @@
         </is>
       </c>
       <c r="B62" s="6" t="n">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C62" s="6" t="n">
         <v>67</v>
       </c>
       <c r="D62" s="6" t="n">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="E62" s="6" t="n">
         <v>0</v>
@@ -2508,16 +2508,16 @@
         <v>65</v>
       </c>
       <c r="G62" s="6" t="n">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H62" s="6" t="n">
         <v>0</v>
       </c>
       <c r="I62" s="5" t="n">
-        <v>-164.99</v>
+        <v>-166.89</v>
       </c>
       <c r="J62" s="5" t="n">
-        <v>-164.99</v>
+        <v>-166.89</v>
       </c>
     </row>
     <row r="63"/>
@@ -2618,20 +2618,20 @@
         </is>
       </c>
       <c r="B6" s="9" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C6" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D6" s="11" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="E6" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="8" t="inlineStr">
         <is>
-          <t>334 trades / 4 market days</t>
+          <t>337 trades / 4 market days</t>
         </is>
       </c>
     </row>
@@ -2642,20 +2642,20 @@
         </is>
       </c>
       <c r="B7" s="12" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="C7" s="13" t="n">
-        <v>0.1676646706586826</v>
+        <v>0.1750741839762611</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-0.5</v>
+        <v>-0.45</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>-0.04</v>
+        <v>0</v>
       </c>
       <c r="F7" s="6" t="inlineStr">
         <is>
-          <t>56 trades / 4 market days</t>
+          <t>59 trades / 4 market days</t>
         </is>
       </c>
     </row>
@@ -2669,13 +2669,13 @@
         <v>62</v>
       </c>
       <c r="C8" s="13" t="n">
-        <v>0.1856287425149701</v>
+        <v>0.1839762611275964</v>
       </c>
       <c r="D8" s="5" t="n">
         <v>-0.62</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>-0.16</v>
+        <v>-0.17</v>
       </c>
       <c r="F8" s="6" t="inlineStr">
         <is>
@@ -2693,13 +2693,13 @@
         <v>82</v>
       </c>
       <c r="C9" s="13" t="n">
-        <v>0.2455089820359281</v>
+        <v>0.2433234421364985</v>
       </c>
       <c r="D9" s="5" t="n">
         <v>-0.37</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="F9" s="6" t="inlineStr">
         <is>
@@ -2717,13 +2717,13 @@
         <v>102</v>
       </c>
       <c r="C10" s="13" t="n">
-        <v>0.3053892215568862</v>
+        <v>0.3026706231454006</v>
       </c>
       <c r="D10" s="5" t="n">
         <v>-0.42</v>
       </c>
       <c r="E10" s="5" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F10" s="6" t="inlineStr">
         <is>
@@ -2741,13 +2741,13 @@
         <v>32</v>
       </c>
       <c r="C11" s="13" t="n">
-        <v>0.09580838323353294</v>
+        <v>0.09495548961424333</v>
       </c>
       <c r="D11" s="5" t="n">
         <v>-0.44</v>
       </c>
       <c r="E11" s="5" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F11" s="6" t="inlineStr">
         <is>
@@ -2803,20 +2803,20 @@
         </is>
       </c>
       <c r="B16" s="9" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C16" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D16" s="11" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="E16" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>334 trades / 4 market days</t>
+          <t>337 trades / 4 market days</t>
         </is>
       </c>
     </row>
@@ -2827,20 +2827,20 @@
         </is>
       </c>
       <c r="B17" s="12" t="n">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="C17" s="13" t="n">
-        <v>0.2904191616766467</v>
+        <v>0.2967359050445104</v>
       </c>
       <c r="D17" s="5" t="n">
-        <v>-0.5600000000000001</v>
+        <v>-0.53</v>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-0.1</v>
+        <v>-0.08</v>
       </c>
       <c r="F17" s="6" t="inlineStr">
         <is>
-          <t>97 trades / 4 market days</t>
+          <t>100 trades / 4 market days</t>
         </is>
       </c>
     </row>
@@ -2854,13 +2854,13 @@
         <v>237</v>
       </c>
       <c r="C18" s="13" t="n">
-        <v>0.7095808383233533</v>
+        <v>0.7032640949554896</v>
       </c>
       <c r="D18" s="5" t="n">
         <v>-0.42</v>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.04</v>
+        <v>0.03</v>
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
@@ -2916,20 +2916,20 @@
         </is>
       </c>
       <c r="B23" s="9" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C23" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D23" s="11" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="E23" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>334 trades / 4 market days</t>
+          <t>337 trades / 4 market days</t>
         </is>
       </c>
     </row>
@@ -2940,20 +2940,20 @@
         </is>
       </c>
       <c r="B24" s="12" t="n">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="C24" s="13" t="n">
-        <v>0.4970059880239521</v>
+        <v>0.4985163204747775</v>
       </c>
       <c r="D24" s="5" t="n">
-        <v>-0.78</v>
+        <v>-0.77</v>
       </c>
       <c r="E24" s="5" t="n">
-        <v>-0.32</v>
+        <v>-0.31</v>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>166 trades / 4 market days</t>
+          <t>168 trades / 4 market days</t>
         </is>
       </c>
     </row>
@@ -2964,20 +2964,20 @@
         </is>
       </c>
       <c r="B25" s="12" t="n">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C25" s="13" t="n">
-        <v>0.5029940119760479</v>
+        <v>0.5014836795252225</v>
       </c>
       <c r="D25" s="5" t="n">
-        <v>-0.15</v>
+        <v>-0.14</v>
       </c>
       <c r="E25" s="5" t="n">
-        <v>0.32</v>
+        <v>0.31</v>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>168 trades / 4 market days</t>
+          <t>169 trades / 4 market days</t>
         </is>
       </c>
     </row>
@@ -3029,20 +3029,20 @@
         </is>
       </c>
       <c r="B30" s="9" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C30" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D30" s="11" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="E30" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>334 trades / 4 market days</t>
+          <t>337 trades / 4 market days</t>
         </is>
       </c>
     </row>
@@ -3056,13 +3056,13 @@
         <v>123</v>
       </c>
       <c r="C31" s="13" t="n">
-        <v>0.3682634730538922</v>
+        <v>0.3649851632047478</v>
       </c>
       <c r="D31" s="5" t="n">
         <v>-0.41</v>
       </c>
       <c r="E31" s="5" t="n">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="F31" s="6" t="inlineStr">
         <is>
@@ -3077,20 +3077,20 @@
         </is>
       </c>
       <c r="B32" s="12" t="n">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="C32" s="13" t="n">
-        <v>0.6317365269461078</v>
+        <v>0.6350148367952523</v>
       </c>
       <c r="D32" s="5" t="n">
-        <v>-0.49</v>
+        <v>-0.48</v>
       </c>
       <c r="E32" s="5" t="n">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>211 trades / 4 market days</t>
+          <t>214 trades / 4 market days</t>
         </is>
       </c>
     </row>
@@ -3150,20 +3150,20 @@
         </is>
       </c>
       <c r="B39" s="9" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C39" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D39" s="11" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="E39" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>334 trades / 4 market days</t>
+          <t>337 trades / 4 market days</t>
         </is>
       </c>
     </row>
@@ -3174,20 +3174,20 @@
         </is>
       </c>
       <c r="B40" s="12" t="n">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="C40" s="13" t="n">
-        <v>0.3682634730538922</v>
+        <v>0.3738872403560831</v>
       </c>
       <c r="D40" s="5" t="n">
-        <v>-0.4</v>
+        <v>-0.38</v>
       </c>
       <c r="E40" s="5" t="n">
-        <v>0.06</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>123 trades / 4 market days</t>
+          <t>126 trades / 4 market days</t>
         </is>
       </c>
     </row>
@@ -3201,13 +3201,13 @@
         <v>94</v>
       </c>
       <c r="C41" s="13" t="n">
-        <v>0.281437125748503</v>
+        <v>0.2789317507418398</v>
       </c>
       <c r="D41" s="5" t="n">
         <v>-0.47</v>
       </c>
       <c r="E41" s="5" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="F41" s="6" t="inlineStr">
         <is>
@@ -3225,7 +3225,7 @@
         <v>68</v>
       </c>
       <c r="C42" s="13" t="n">
-        <v>0.2035928143712575</v>
+        <v>0.2017804154302671</v>
       </c>
       <c r="D42" s="5" t="n">
         <v>-0.53</v>
@@ -3249,7 +3249,7 @@
         <v>49</v>
       </c>
       <c r="C43" s="13" t="n">
-        <v>0.1467065868263473</v>
+        <v>0.1454005934718101</v>
       </c>
       <c r="D43" s="5" t="n">
         <v>-0.5</v>
@@ -3311,20 +3311,20 @@
         </is>
       </c>
       <c r="B48" s="9" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C48" s="10" t="n">
         <v>1</v>
       </c>
       <c r="D48" s="11" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="E48" s="11" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>334 trades / 4 market days</t>
+          <t>337 trades / 4 market days</t>
         </is>
       </c>
     </row>
@@ -3335,20 +3335,20 @@
         </is>
       </c>
       <c r="B49" s="12" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C49" s="13" t="n">
         <v>1</v>
       </c>
       <c r="D49" s="5" t="n">
-        <v>-0.46</v>
+        <v>-0.45</v>
       </c>
       <c r="E49" s="5" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>334 trades / 4 market days</t>
+          <t>337 trades / 4 market days</t>
         </is>
       </c>
     </row>
@@ -3395,7 +3395,7 @@
         </is>
       </c>
       <c r="B54" s="12" t="n">
-        <v>334</v>
+        <v>337</v>
       </c>
       <c r="C54" s="12" t="n">
         <v>43</v>
@@ -3404,7 +3404,7 @@
         <v>224</v>
       </c>
       <c r="E54" s="12" t="n">
-        <v>67</v>
+        <v>70</v>
       </c>
     </row>
   </sheetData>
@@ -14735,16 +14735,20 @@
       </c>
       <c r="M130" s="6" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N130" s="6" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="N130" s="5" t="n">
+        <v>1.77</v>
+      </c>
       <c r="O130" s="6" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P130" s="6" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="P130" s="5" t="n">
+        <v>2.9</v>
+      </c>
       <c r="Q130" s="6" t="inlineStr">
         <is>
           <t>pending</t>
@@ -31375,16 +31379,20 @@
       </c>
       <c r="M348" s="6" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N348" s="6" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="N348" s="5" t="n">
+        <v>0.29</v>
+      </c>
       <c r="O348" s="6" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P348" s="6" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="P348" s="5" t="n">
+        <v>0</v>
+      </c>
       <c r="Q348" s="6" t="inlineStr">
         <is>
           <t>pending</t>
@@ -31837,10 +31845,12 @@
       </c>
       <c r="M354" s="6" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N354" s="6" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="N354" s="5" t="n">
+        <v>0.42</v>
+      </c>
       <c r="O354" s="6" t="inlineStr">
         <is>
           <t>pending</t>
@@ -39073,16 +39083,20 @@
       </c>
       <c r="O449" s="6" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="P449" s="6" t="n"/>
+          <t>timeout</t>
+        </is>
+      </c>
+      <c r="P449" s="5" t="n">
+        <v>1.33</v>
+      </c>
       <c r="Q449" s="6" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="R449" s="6" t="n"/>
+          <t>stop</t>
+        </is>
+      </c>
+      <c r="R449" s="5" t="n">
+        <v>-1.8</v>
+      </c>
     </row>
     <row r="450">
       <c r="A450" s="6" t="inlineStr">

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -224,12 +224,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily'!$A$2:$A$5</f>
+              <f>'Daily'!$A$2:$A$6</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily'!$B$2:$B$5</f>
+              <f>'Daily'!$B$2:$B$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R26"/>
+  <dimension ref="A1:R36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -645,17 +645,17 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-23 20:16 UK time. The live mock trader enters ideas as they trigger during the day: one new trade per scan, up to 5 a day (3 a day before 23 Oct 2026), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="15" customHeight="1">
+          <t>Generated 2026-10-26 17:08 UK time. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Each trade is £100. Dealing costs = 0.10% (buy and sell together); stamp duty = 0.50% on buys of real shares (sells never pay it). Grey rows were never entered or have no result yet.</t>
+          <t>Each trade is £100. Dealing costs = 0.10% (buy and sell together); stamp duty = 0.50% on buys of real shares (sells never pay it). Grey rows were never entered or have no result yet. Results rechecked with version 3 missing-price safeguards; older totals may differ. Only resolved trades enter the totals.</t>
         </is>
       </c>
     </row>
@@ -708,28 +708,28 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>0.32</v>
+        <v>-2.62</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>3.52</v>
+        <v>1.48</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-1.2</v>
+        <v>-2.1</v>
       </c>
       <c r="I5" s="4" t="n">
         <v>-2</v>
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>0.03</v>
+        <v>-0.12</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>677</v>
+        <v>728</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.33</v>
+        <v>-0.32</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.35</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -1753,96 +1753,793 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="12" t="inlineStr">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C25" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" s="8" t="inlineStr">
+        <is>
+          <t>Pearson plc</t>
+        </is>
+      </c>
+      <c r="E25" s="8" t="inlineStr">
+        <is>
+          <t>PSON.L</t>
+        </is>
+      </c>
+      <c r="F25" s="8" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G25" s="8" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="H25" s="8" t="n">
+        <v>1368.5</v>
+      </c>
+      <c r="I25" s="8" t="n">
+        <v>1376.75</v>
+      </c>
+      <c r="J25" s="8" t="n">
+        <v>1337.7</v>
+      </c>
+      <c r="K25" s="8" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L25" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26 09:15</t>
+        </is>
+      </c>
+      <c r="M25" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N25" s="9" t="n">
+        <v>-0.6</v>
+      </c>
+      <c r="O25" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P25" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q25" s="9" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="R25" s="9" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B26" s="8" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="C26" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D26" s="8" t="inlineStr">
+        <is>
+          <t>IG Group</t>
+        </is>
+      </c>
+      <c r="E26" s="8" t="inlineStr">
+        <is>
+          <t>IGG.L</t>
+        </is>
+      </c>
+      <c r="F26" s="8" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G26" s="8" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="H26" s="8" t="n">
+        <v>945.5</v>
+      </c>
+      <c r="I26" s="8" t="n">
+        <v>955.7</v>
+      </c>
+      <c r="J26" s="8" t="n">
+        <v>940.89</v>
+      </c>
+      <c r="K26" s="8" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L26" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26 11:45</t>
+        </is>
+      </c>
+      <c r="M26" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N26" s="9" t="n">
+        <v>-1.08</v>
+      </c>
+      <c r="O26" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P26" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q26" s="9" t="n">
+        <v>-1.18</v>
+      </c>
+      <c r="R26" s="9" t="n">
+        <v>-1.56</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B27" s="8" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="C27" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="D27" s="8" t="inlineStr">
+        <is>
+          <t>Reckitt</t>
+        </is>
+      </c>
+      <c r="E27" s="8" t="inlineStr">
+        <is>
+          <t>RKT.L</t>
+        </is>
+      </c>
+      <c r="F27" s="8" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G27" s="8" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="H27" s="8" t="n">
+        <v>5528</v>
+      </c>
+      <c r="I27" s="8" t="n">
+        <v>5542.75</v>
+      </c>
+      <c r="J27" s="8" t="n">
+        <v>5499.75</v>
+      </c>
+      <c r="K27" s="8" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L27" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:30</t>
+        </is>
+      </c>
+      <c r="M27" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N27" s="9" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="O27" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P27" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q27" s="9" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="R27" s="9" t="n">
+        <v>-1.93</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="C28" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D28" s="8" t="inlineStr">
+        <is>
+          <t>Imperial Brands</t>
+        </is>
+      </c>
+      <c r="E28" s="8" t="inlineStr">
+        <is>
+          <t>IMB.L</t>
+        </is>
+      </c>
+      <c r="F28" s="8" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G28" s="8" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="H28" s="8" t="n">
+        <v>2851</v>
+      </c>
+      <c r="I28" s="8" t="n">
+        <v>2862.5</v>
+      </c>
+      <c r="J28" s="8" t="n">
+        <v>2840.5</v>
+      </c>
+      <c r="K28" s="8" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L28" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:45</t>
+        </is>
+      </c>
+      <c r="M28" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N28" s="9" t="n">
+        <v>-0.4</v>
+      </c>
+      <c r="O28" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P28" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q28" s="9" t="n">
+        <v>-0.5</v>
+      </c>
+      <c r="R28" s="9" t="n">
+        <v>-2.43</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="C29" s="8" t="n">
+        <v>6</v>
+      </c>
+      <c r="D29" s="8" t="inlineStr">
+        <is>
+          <t>IHG Hotels &amp; Resorts</t>
+        </is>
+      </c>
+      <c r="E29" s="8" t="inlineStr">
+        <is>
+          <t>IHG.L</t>
+        </is>
+      </c>
+      <c r="F29" s="8" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G29" s="8" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="H29" s="8" t="n">
+        <v>166.25</v>
+      </c>
+      <c r="I29" s="8" t="n">
+        <v>166.7</v>
+      </c>
+      <c r="J29" s="8" t="n">
+        <v>163.5</v>
+      </c>
+      <c r="K29" s="8" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L29" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26 13:45</t>
+        </is>
+      </c>
+      <c r="M29" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N29" s="9" t="n">
+        <v>-0.27</v>
+      </c>
+      <c r="O29" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P29" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q29" s="9" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="R29" s="9" t="n">
+        <v>-2.8</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="C30" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D30" s="8" t="inlineStr">
+        <is>
+          <t>Smiths Group</t>
+        </is>
+      </c>
+      <c r="E30" s="8" t="inlineStr">
+        <is>
+          <t>SMIN.L</t>
+        </is>
+      </c>
+      <c r="F30" s="8" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G30" s="8" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="H30" s="8" t="n">
+        <v>2648</v>
+      </c>
+      <c r="I30" s="8" t="n">
+        <v>2654</v>
+      </c>
+      <c r="J30" s="8" t="n">
+        <v>2634</v>
+      </c>
+      <c r="K30" s="8" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L30" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:30</t>
+        </is>
+      </c>
+      <c r="M30" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N30" s="9" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="O30" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P30" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="9" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="R30" s="9" t="n">
+        <v>-3.13</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B31" s="8" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="C31" s="8" t="n">
+        <v>2</v>
+      </c>
+      <c r="D31" s="8" t="inlineStr">
+        <is>
+          <t>Coca-Cola HBC</t>
+        </is>
+      </c>
+      <c r="E31" s="8" t="inlineStr">
+        <is>
+          <t>CCH.L</t>
+        </is>
+      </c>
+      <c r="F31" s="8" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G31" s="8" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="H31" s="8" t="n">
+        <v>4532</v>
+      </c>
+      <c r="I31" s="8" t="n">
+        <v>4548.75</v>
+      </c>
+      <c r="J31" s="8" t="n">
+        <v>4440.6</v>
+      </c>
+      <c r="K31" s="8" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L31" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26 14:45</t>
+        </is>
+      </c>
+      <c r="M31" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N31" s="9" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="O31" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P31" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q31" s="9" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="R31" s="9" t="n">
+        <v>-3.6</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B32" s="10" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D32" s="10" t="inlineStr">
+        <is>
+          <t>Games Workshop</t>
+        </is>
+      </c>
+      <c r="E32" s="10" t="inlineStr">
+        <is>
+          <t>GAW.L</t>
+        </is>
+      </c>
+      <c r="F32" s="10" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G32" s="10" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="H32" s="10" t="n">
+        <v>16220</v>
+      </c>
+      <c r="I32" s="10" t="n">
+        <v>16356.25</v>
+      </c>
+      <c r="J32" s="10" t="n">
+        <v>16011.25</v>
+      </c>
+      <c r="K32" s="10" t="inlineStr">
+        <is>
+          <t>Target hit</t>
+        </is>
+      </c>
+      <c r="L32" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:00</t>
+        </is>
+      </c>
+      <c r="M32" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N32" s="11" t="n">
+        <v>1.29</v>
+      </c>
+      <c r="O32" s="11" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P32" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="11" t="n">
+        <v>1.19</v>
+      </c>
+      <c r="R32" s="11" t="n">
+        <v>-2.41</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="C33" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D33" s="8" t="inlineStr">
+        <is>
+          <t>Hiscox</t>
+        </is>
+      </c>
+      <c r="E33" s="8" t="inlineStr">
+        <is>
+          <t>HSX.L</t>
+        </is>
+      </c>
+      <c r="F33" s="8" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G33" s="8" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="H33" s="8" t="n">
+        <v>1829</v>
+      </c>
+      <c r="I33" s="8" t="n">
+        <v>1833.25</v>
+      </c>
+      <c r="J33" s="8" t="n">
+        <v>1808.25</v>
+      </c>
+      <c r="K33" s="8" t="inlineStr">
+        <is>
+          <t>Closed at end of day</t>
+        </is>
+      </c>
+      <c r="L33" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-26 16:30</t>
+        </is>
+      </c>
+      <c r="M33" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N33" s="9" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="O33" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P33" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q33" s="9" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="R33" s="9" t="n">
+        <v>-2.62</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="12" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B25" s="12" t="inlineStr">
+      <c r="B34" s="12" t="inlineStr">
         <is>
           <t>08:32</t>
         </is>
       </c>
-      <c r="C25" s="12" t="n">
+      <c r="C34" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D25" s="12" t="inlineStr">
+      <c r="D34" s="12" t="inlineStr">
         <is>
           <t>Hammerson</t>
         </is>
       </c>
-      <c r="E25" s="12" t="inlineStr">
+      <c r="E34" s="12" t="inlineStr">
         <is>
           <t>HMSO.L</t>
         </is>
       </c>
-      <c r="F25" s="12" t="inlineStr">
+      <c r="F34" s="12" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="G25" s="12" t="inlineStr">
+      <c r="G34" s="12" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="H25" s="12" t="n"/>
-      <c r="I25" s="12" t="n">
+      <c r="H34" s="12" t="n"/>
+      <c r="I34" s="12" t="n">
         <v>346.55</v>
       </c>
-      <c r="J25" s="12" t="n">
+      <c r="J34" s="12" t="n">
         <v>352.35</v>
       </c>
-      <c r="K25" s="12" t="inlineStr">
+      <c r="K34" s="12" t="inlineStr">
         <is>
           <t>Not resolved yet</t>
         </is>
       </c>
     </row>
-    <row r="26">
-      <c r="A26" s="12" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="12" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B26" s="12" t="inlineStr">
+      <c r="B35" s="12" t="inlineStr">
         <is>
           <t>08:47</t>
         </is>
       </c>
-      <c r="C26" s="12" t="n">
+      <c r="C35" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D26" s="12" t="inlineStr">
+      <c r="D35" s="12" t="inlineStr">
         <is>
           <t>ME Group International</t>
         </is>
       </c>
-      <c r="E26" s="12" t="inlineStr">
+      <c r="E35" s="12" t="inlineStr">
         <is>
           <t>MEGP.L</t>
         </is>
       </c>
-      <c r="F26" s="12" t="inlineStr">
+      <c r="F35" s="12" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="G26" s="12" t="inlineStr">
+      <c r="G35" s="12" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="H26" s="12" t="n"/>
-      <c r="I26" s="12" t="n">
+      <c r="H35" s="12" t="n"/>
+      <c r="I35" s="12" t="n">
         <v>112.35</v>
       </c>
-      <c r="J26" s="12" t="n">
+      <c r="J35" s="12" t="n">
         <v>108.54</v>
       </c>
-      <c r="K26" s="12" t="inlineStr">
+      <c r="K35" s="12" t="inlineStr">
         <is>
           <t>Not resolved yet</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B36" s="12" t="inlineStr">
+        <is>
+          <t>12:17</t>
+        </is>
+      </c>
+      <c r="C36" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D36" s="12" t="inlineStr">
+        <is>
+          <t>Severn Trent</t>
+        </is>
+      </c>
+      <c r="E36" s="12" t="inlineStr">
+        <is>
+          <t>SVT.L</t>
+        </is>
+      </c>
+      <c r="F36" s="12" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G36" s="12" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="H36" s="12" t="n">
+        <v>3264</v>
+      </c>
+      <c r="I36" s="12" t="n">
+        <v>3263.99</v>
+      </c>
+      <c r="J36" s="12" t="n">
+        <v>3208.02</v>
+      </c>
+      <c r="K36" s="12" t="inlineStr">
+        <is>
+          <t>Skipped (price already past stop or target)</t>
         </is>
       </c>
     </row>
@@ -1862,7 +2559,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1877,7 +2574,7 @@
       </c>
       <c r="B1" s="3" t="inlineStr">
         <is>
-          <t>Live: trades at trigger points (up to 5 a day) (cumulative £)</t>
+          <t>Live: trades at trigger points (cumulative £)</t>
         </is>
       </c>
     </row>
@@ -1921,10 +2618,20 @@
         <v>0.32</v>
       </c>
     </row>
-    <row r="6"/>
+    <row r="6">
+      <c r="A6" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-26</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-2.62</v>
+      </c>
+    </row>
     <row r="7"/>
-    <row r="8">
-      <c r="A8" s="5" t="inlineStr">
+    <row r="8"/>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
         <is>
           <t>Each trade is £100, after dealing costs and stamp duty.</t>
         </is>

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -648,7 +648,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 17:08 UK time. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
+          <t>Generated 2026-10-26 20:31 UK time. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
         </is>
       </c>
     </row>

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -648,7 +648,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 20:31 UK time. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
+          <t>Generated 2026-10-26 20:45 UK time. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
         </is>
       </c>
     </row>

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -224,12 +224,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily'!$A$2:$A$6</f>
+              <f>'Daily'!$A$2:$A$7</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily'!$B$2:$B$6</f>
+              <f>'Daily'!$B$2:$B$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R36"/>
+  <dimension ref="A1:R46"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -648,14 +648,14 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-26 20:45 UK time. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
+          <t>Generated 2026-10-27 17:07 UK time. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Each trade is £100. Dealing costs = 0.10% (buy and sell together); stamp duty = 0.50% on buys of real shares (sells never pay it). Grey rows were never entered or have no result yet. Results rechecked with version 3 missing-price safeguards; older totals may differ. Only resolved trades enter the totals.</t>
+          <t>Each trade is £100. Dealing costs = 0.10% (buy and sell together); stamp duty = 0.00% on buys (0 = spread bet, the basis for all results from 26 Oct 2026, including earlier trades). Grey rows were never entered or have no result yet. Results rechecked with version 3 missing-price safeguards; older totals may differ. Only resolved trades enter the totals.</t>
         </is>
       </c>
     </row>
@@ -708,31 +708,31 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>-2.62</v>
+        <v>-1.07</v>
       </c>
       <c r="B5" s="1" t="n">
+        <v>29</v>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1" t="n">
         <v>21</v>
-      </c>
-      <c r="C5" s="1" t="n">
-        <v>5</v>
-      </c>
-      <c r="D5" s="1" t="n">
-        <v>16</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="1" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1.48</v>
+        <v>1.83</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-2.1</v>
+        <v>-2.9</v>
       </c>
       <c r="I5" s="4" t="n">
-        <v>-2</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="7" ht="32" customHeight="1">
@@ -774,19 +774,19 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.12</v>
+        <v>-0.04</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>728</v>
+        <v>862</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.32</v>
+        <v>-0.08</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.2</v>
+        <v>0.05</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -951,13 +951,13 @@
         <v>-0.1</v>
       </c>
       <c r="P13" s="9" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="Q13" s="9" t="n">
-        <v>-1.01</v>
+        <v>-0.51</v>
       </c>
       <c r="R13" s="9" t="n">
-        <v>-1.01</v>
+        <v>-0.51</v>
       </c>
     </row>
     <row r="14">
@@ -1029,7 +1029,7 @@
         <v>-0.68</v>
       </c>
       <c r="R14" s="9" t="n">
-        <v>-1.69</v>
+        <v>-1.19</v>
       </c>
     </row>
     <row r="15">
@@ -1095,13 +1095,13 @@
         <v>-0.1</v>
       </c>
       <c r="P15" s="9" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="9" t="n">
-        <v>-1.22</v>
+        <v>-0.72</v>
       </c>
       <c r="R15" s="9" t="n">
-        <v>-2.91</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="16">
@@ -1167,13 +1167,13 @@
         <v>-0.1</v>
       </c>
       <c r="P16" s="9" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="9" t="n">
-        <v>-0.89</v>
+        <v>-0.39</v>
       </c>
       <c r="R16" s="9" t="n">
-        <v>-3.8</v>
+        <v>-2.3</v>
       </c>
     </row>
     <row r="17">
@@ -1239,13 +1239,13 @@
         <v>-0.1</v>
       </c>
       <c r="P17" s="9" t="n">
-        <v>-0.5</v>
+        <v>0</v>
       </c>
       <c r="Q17" s="9" t="n">
-        <v>-0.8100000000000001</v>
+        <v>-0.31</v>
       </c>
       <c r="R17" s="9" t="n">
-        <v>-4.61</v>
+        <v>-2.61</v>
       </c>
     </row>
     <row r="18">
@@ -1317,7 +1317,7 @@
         <v>1.68</v>
       </c>
       <c r="R18" s="11" t="n">
-        <v>-2.93</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="19">
@@ -1389,7 +1389,7 @@
         <v>1.61</v>
       </c>
       <c r="R19" s="11" t="n">
-        <v>-1.32</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="20">
@@ -1461,7 +1461,7 @@
         <v>-0.44</v>
       </c>
       <c r="R20" s="9" t="n">
-        <v>-1.76</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="21">
@@ -1533,7 +1533,7 @@
         <v>2.88</v>
       </c>
       <c r="R21" s="11" t="n">
-        <v>1.12</v>
+        <v>3.12</v>
       </c>
     </row>
     <row r="22">
@@ -1605,7 +1605,7 @@
         <v>-0.47</v>
       </c>
       <c r="R22" s="9" t="n">
-        <v>0.65</v>
+        <v>2.65</v>
       </c>
     </row>
     <row r="23">
@@ -1677,7 +1677,7 @@
         <v>-0.52</v>
       </c>
       <c r="R23" s="9" t="n">
-        <v>0.13</v>
+        <v>2.13</v>
       </c>
     </row>
     <row r="24">
@@ -1749,7 +1749,7 @@
         <v>0.19</v>
       </c>
       <c r="R24" s="11" t="n">
-        <v>0.32</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="25">
@@ -1821,7 +1821,7 @@
         <v>-0.7</v>
       </c>
       <c r="R25" s="9" t="n">
-        <v>-0.38</v>
+        <v>1.62</v>
       </c>
     </row>
     <row r="26">
@@ -1893,7 +1893,7 @@
         <v>-1.18</v>
       </c>
       <c r="R26" s="9" t="n">
-        <v>-1.56</v>
+        <v>0.44</v>
       </c>
     </row>
     <row r="27">
@@ -1965,7 +1965,7 @@
         <v>-0.37</v>
       </c>
       <c r="R27" s="9" t="n">
-        <v>-1.93</v>
+        <v>0.07000000000000001</v>
       </c>
     </row>
     <row r="28">
@@ -2037,7 +2037,7 @@
         <v>-0.5</v>
       </c>
       <c r="R28" s="9" t="n">
-        <v>-2.43</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="29">
@@ -2109,7 +2109,7 @@
         <v>-0.37</v>
       </c>
       <c r="R29" s="9" t="n">
-        <v>-2.8</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="30">
@@ -2181,7 +2181,7 @@
         <v>-0.33</v>
       </c>
       <c r="R30" s="9" t="n">
-        <v>-3.13</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="31">
@@ -2253,7 +2253,7 @@
         <v>-0.47</v>
       </c>
       <c r="R31" s="9" t="n">
-        <v>-3.6</v>
+        <v>-1.6</v>
       </c>
     </row>
     <row r="32">
@@ -2325,7 +2325,7 @@
         <v>1.19</v>
       </c>
       <c r="R32" s="11" t="n">
-        <v>-2.41</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="33">
@@ -2397,147 +2397,821 @@
         <v>-0.21</v>
       </c>
       <c r="R33" s="9" t="n">
-        <v>-2.62</v>
+        <v>-0.62</v>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="12" t="inlineStr">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C34" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="D34" s="8" t="inlineStr">
+        <is>
+          <t>Segro</t>
+        </is>
+      </c>
+      <c r="E34" s="8" t="inlineStr">
+        <is>
+          <t>SGRO.L</t>
+        </is>
+      </c>
+      <c r="F34" s="8" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G34" s="8" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="H34" s="8" t="n">
+        <v>902.6</v>
+      </c>
+      <c r="I34" s="8" t="n">
+        <v>905.97</v>
+      </c>
+      <c r="J34" s="8" t="n">
+        <v>890.08</v>
+      </c>
+      <c r="K34" s="8" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L34" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:00</t>
+        </is>
+      </c>
+      <c r="M34" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N34" s="9" t="n">
+        <v>-0.37</v>
+      </c>
+      <c r="O34" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P34" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q34" s="9" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="R34" s="9" t="n">
+        <v>-1.09</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C35" s="8" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="8" t="inlineStr">
+        <is>
+          <t>Pearson plc</t>
+        </is>
+      </c>
+      <c r="E35" s="8" t="inlineStr">
+        <is>
+          <t>PSON.L</t>
+        </is>
+      </c>
+      <c r="F35" s="8" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G35" s="8" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="H35" s="8" t="n">
+        <v>1368.5</v>
+      </c>
+      <c r="I35" s="8" t="n">
+        <v>1369.94</v>
+      </c>
+      <c r="J35" s="8" t="n">
+        <v>1346.19</v>
+      </c>
+      <c r="K35" s="8" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L35" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27 09:15</t>
+        </is>
+      </c>
+      <c r="M35" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N35" s="9" t="n">
+        <v>-0.11</v>
+      </c>
+      <c r="O35" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P35" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q35" s="9" t="n">
+        <v>-0.21</v>
+      </c>
+      <c r="R35" s="9" t="n">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>09:47</t>
+        </is>
+      </c>
+      <c r="C36" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D36" s="8" t="inlineStr">
+        <is>
+          <t>IHG Hotels &amp; Resorts</t>
+        </is>
+      </c>
+      <c r="E36" s="8" t="inlineStr">
+        <is>
+          <t>IHG.L</t>
+        </is>
+      </c>
+      <c r="F36" s="8" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G36" s="8" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="H36" s="8" t="n">
+        <v>166.75</v>
+      </c>
+      <c r="I36" s="8" t="n">
+        <v>165.51</v>
+      </c>
+      <c r="J36" s="8" t="n">
+        <v>169.88</v>
+      </c>
+      <c r="K36" s="8" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L36" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:15</t>
+        </is>
+      </c>
+      <c r="M36" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N36" s="9" t="n">
+        <v>-0.74</v>
+      </c>
+      <c r="O36" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P36" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q36" s="9" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="R36" s="9" t="n">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C37" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="D37" s="8" t="inlineStr">
+        <is>
+          <t>Croda International</t>
+        </is>
+      </c>
+      <c r="E37" s="8" t="inlineStr">
+        <is>
+          <t>CRDA.L</t>
+        </is>
+      </c>
+      <c r="F37" s="8" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G37" s="8" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="H37" s="8" t="n">
+        <v>3594</v>
+      </c>
+      <c r="I37" s="8" t="n">
+        <v>3612.75</v>
+      </c>
+      <c r="J37" s="8" t="n">
+        <v>3514.27</v>
+      </c>
+      <c r="K37" s="8" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L37" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:45</t>
+        </is>
+      </c>
+      <c r="M37" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N37" s="9" t="n">
+        <v>-0.52</v>
+      </c>
+      <c r="O37" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P37" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q37" s="9" t="n">
+        <v>-0.62</v>
+      </c>
+      <c r="R37" s="9" t="n">
+        <v>-2.76</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="C38" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="D38" s="8" t="inlineStr">
+        <is>
+          <t>Aberdeen Group</t>
+        </is>
+      </c>
+      <c r="E38" s="8" t="inlineStr">
+        <is>
+          <t>ABDN.L</t>
+        </is>
+      </c>
+      <c r="F38" s="8" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G38" s="8" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="H38" s="8" t="n">
+        <v>218.4</v>
+      </c>
+      <c r="I38" s="8" t="n">
+        <v>219.22</v>
+      </c>
+      <c r="J38" s="8" t="n">
+        <v>216.74</v>
+      </c>
+      <c r="K38" s="8" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L38" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-27 10:45</t>
+        </is>
+      </c>
+      <c r="M38" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N38" s="9" t="n">
+        <v>-0.38</v>
+      </c>
+      <c r="O38" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P38" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="9" t="n">
+        <v>-0.48</v>
+      </c>
+      <c r="R38" s="9" t="n">
+        <v>-3.24</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B39" s="10" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="C39" s="10" t="n">
+        <v>10</v>
+      </c>
+      <c r="D39" s="10" t="inlineStr">
+        <is>
+          <t>LondonMetric Property</t>
+        </is>
+      </c>
+      <c r="E39" s="10" t="inlineStr">
+        <is>
+          <t>LMP.L</t>
+        </is>
+      </c>
+      <c r="F39" s="10" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G39" s="10" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="H39" s="10" t="n">
+        <v>182.8</v>
+      </c>
+      <c r="I39" s="10" t="n">
+        <v>181.48</v>
+      </c>
+      <c r="J39" s="10" t="n">
+        <v>183.17</v>
+      </c>
+      <c r="K39" s="10" t="inlineStr">
+        <is>
+          <t>Target hit</t>
+        </is>
+      </c>
+      <c r="L39" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-27 14:45</t>
+        </is>
+      </c>
+      <c r="M39" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N39" s="11" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="O39" s="11" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P39" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q39" s="11" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="R39" s="11" t="n">
+        <v>-3.14</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B40" s="10" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C40" s="10" t="n">
+        <v>5</v>
+      </c>
+      <c r="D40" s="10" t="inlineStr">
+        <is>
+          <t>Halma plc</t>
+        </is>
+      </c>
+      <c r="E40" s="10" t="inlineStr">
+        <is>
+          <t>HLMA.L</t>
+        </is>
+      </c>
+      <c r="F40" s="10" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G40" s="10" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="H40" s="10" t="n">
+        <v>3320</v>
+      </c>
+      <c r="I40" s="10" t="n">
+        <v>3292.05</v>
+      </c>
+      <c r="J40" s="10" t="n">
+        <v>3384.36</v>
+      </c>
+      <c r="K40" s="10" t="inlineStr">
+        <is>
+          <t>Target hit</t>
+        </is>
+      </c>
+      <c r="L40" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-27 16:15</t>
+        </is>
+      </c>
+      <c r="M40" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N40" s="11" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="O40" s="11" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P40" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q40" s="11" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="R40" s="11" t="n">
+        <v>-1.3</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B41" s="10" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="C41" s="10" t="n">
+        <v>7</v>
+      </c>
+      <c r="D41" s="10" t="inlineStr">
+        <is>
+          <t>Investec</t>
+        </is>
+      </c>
+      <c r="E41" s="10" t="inlineStr">
+        <is>
+          <t>INVP.L</t>
+        </is>
+      </c>
+      <c r="F41" s="10" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G41" s="10" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="H41" s="10" t="n">
+        <v>610.5</v>
+      </c>
+      <c r="I41" s="10" t="n">
+        <v>605.12</v>
+      </c>
+      <c r="J41" s="10" t="n">
+        <v>620.0599999999999</v>
+      </c>
+      <c r="K41" s="10" t="inlineStr">
+        <is>
+          <t>Closed at end of day</t>
+        </is>
+      </c>
+      <c r="L41" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-27 16:30</t>
+        </is>
+      </c>
+      <c r="M41" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N41" s="11" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="O41" s="11" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P41" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q41" s="11" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="R41" s="11" t="n">
+        <v>-1.07</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="12" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B34" s="12" t="inlineStr">
+      <c r="B42" s="12" t="inlineStr">
         <is>
           <t>08:32</t>
         </is>
       </c>
-      <c r="C34" s="12" t="n">
+      <c r="C42" s="12" t="n">
         <v>2</v>
       </c>
-      <c r="D34" s="12" t="inlineStr">
+      <c r="D42" s="12" t="inlineStr">
         <is>
           <t>Hammerson</t>
         </is>
       </c>
-      <c r="E34" s="12" t="inlineStr">
+      <c r="E42" s="12" t="inlineStr">
         <is>
           <t>HMSO.L</t>
         </is>
       </c>
-      <c r="F34" s="12" t="inlineStr">
+      <c r="F42" s="12" t="inlineStr">
         <is>
           <t>Long</t>
         </is>
       </c>
-      <c r="G34" s="12" t="inlineStr">
+      <c r="G42" s="12" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="H34" s="12" t="n"/>
-      <c r="I34" s="12" t="n">
+      <c r="H42" s="12" t="n"/>
+      <c r="I42" s="12" t="n">
         <v>346.55</v>
       </c>
-      <c r="J34" s="12" t="n">
+      <c r="J42" s="12" t="n">
         <v>352.35</v>
       </c>
-      <c r="K34" s="12" t="inlineStr">
+      <c r="K42" s="12" t="inlineStr">
         <is>
           <t>Not resolved yet</t>
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="12" t="inlineStr">
         <is>
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="B35" s="12" t="inlineStr">
+      <c r="B43" s="12" t="inlineStr">
         <is>
           <t>08:47</t>
         </is>
       </c>
-      <c r="C35" s="12" t="n">
+      <c r="C43" s="12" t="n">
         <v>3</v>
       </c>
-      <c r="D35" s="12" t="inlineStr">
+      <c r="D43" s="12" t="inlineStr">
         <is>
           <t>ME Group International</t>
         </is>
       </c>
-      <c r="E35" s="12" t="inlineStr">
+      <c r="E43" s="12" t="inlineStr">
         <is>
           <t>MEGP.L</t>
         </is>
       </c>
-      <c r="F35" s="12" t="inlineStr">
+      <c r="F43" s="12" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="G35" s="12" t="inlineStr">
+      <c r="G43" s="12" t="inlineStr">
         <is>
           <t>Range</t>
         </is>
       </c>
-      <c r="H35" s="12" t="n"/>
-      <c r="I35" s="12" t="n">
+      <c r="H43" s="12" t="n"/>
+      <c r="I43" s="12" t="n">
         <v>112.35</v>
       </c>
-      <c r="J35" s="12" t="n">
+      <c r="J43" s="12" t="n">
         <v>108.54</v>
       </c>
-      <c r="K35" s="12" t="inlineStr">
+      <c r="K43" s="12" t="inlineStr">
         <is>
           <t>Not resolved yet</t>
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="12" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="12" t="inlineStr">
         <is>
           <t>2026-10-26</t>
         </is>
       </c>
-      <c r="B36" s="12" t="inlineStr">
+      <c r="B44" s="12" t="inlineStr">
         <is>
           <t>12:17</t>
         </is>
       </c>
-      <c r="C36" s="12" t="n">
+      <c r="C44" s="12" t="n">
         <v>5</v>
       </c>
-      <c r="D36" s="12" t="inlineStr">
+      <c r="D44" s="12" t="inlineStr">
         <is>
           <t>Severn Trent</t>
         </is>
       </c>
-      <c r="E36" s="12" t="inlineStr">
+      <c r="E44" s="12" t="inlineStr">
         <is>
           <t>SVT.L</t>
         </is>
       </c>
-      <c r="F36" s="12" t="inlineStr">
+      <c r="F44" s="12" t="inlineStr">
         <is>
           <t>Short</t>
         </is>
       </c>
-      <c r="G36" s="12" t="inlineStr">
+      <c r="G44" s="12" t="inlineStr">
         <is>
           <t>Breakout</t>
         </is>
       </c>
-      <c r="H36" s="12" t="n">
+      <c r="H44" s="12" t="n">
         <v>3264</v>
       </c>
-      <c r="I36" s="12" t="n">
+      <c r="I44" s="12" t="n">
         <v>3263.99</v>
       </c>
-      <c r="J36" s="12" t="n">
+      <c r="J44" s="12" t="n">
         <v>3208.02</v>
       </c>
-      <c r="K36" s="12" t="inlineStr">
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>Skipped (price already past stop or target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B45" s="12" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C45" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>Whitbread</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>WTB.L</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="n">
+        <v>2583.22</v>
+      </c>
+      <c r="I45" s="12" t="n">
+        <v>2580.12</v>
+      </c>
+      <c r="J45" s="12" t="n">
+        <v>2555.62</v>
+      </c>
+      <c r="K45" s="12" t="inlineStr">
+        <is>
+          <t>Skipped (price already past stop or target)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="12" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B46" s="12" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="C46" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>Hiscox</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>HSX.L</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="n">
+        <v>1839</v>
+      </c>
+      <c r="I46" s="12" t="n">
+        <v>1836.75</v>
+      </c>
+      <c r="J46" s="12" t="n">
+        <v>1821.75</v>
+      </c>
+      <c r="K46" s="12" t="inlineStr">
         <is>
           <t>Skipped (price already past stop or target)</t>
         </is>
@@ -2559,7 +3233,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2585,7 +3259,7 @@
         </is>
       </c>
       <c r="B2" s="6" t="n">
-        <v>-2.91</v>
+        <v>-1.91</v>
       </c>
     </row>
     <row r="3">
@@ -2595,7 +3269,7 @@
         </is>
       </c>
       <c r="B3" s="6" t="n">
-        <v>-2.93</v>
+        <v>-0.93</v>
       </c>
     </row>
     <row r="4">
@@ -2605,7 +3279,7 @@
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>-1.32</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="5">
@@ -2615,7 +3289,7 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>0.32</v>
+        <v>2.32</v>
       </c>
     </row>
     <row r="6">
@@ -2625,13 +3299,23 @@
         </is>
       </c>
       <c r="B6" s="6" t="n">
-        <v>-2.62</v>
-      </c>
-    </row>
-    <row r="7"/>
+        <v>-0.62</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-27</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>-1.07</v>
+      </c>
+    </row>
     <row r="8"/>
-    <row r="9">
-      <c r="A9" s="5" t="inlineStr">
+    <row r="9"/>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
         <is>
           <t>Each trade is £100, after dealing costs and stamp duty.</t>
         </is>

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -81,7 +81,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -100,7 +100,6 @@
     <xf numFmtId="164" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -615,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R46"/>
+  <dimension ref="A1:R41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -648,14 +647,14 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-27 17:07 UK time. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="30" customHeight="1">
+          <t>Generated 2026-10-27 21:29 UK time. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Each trade is £100. Dealing costs = 0.10% (buy and sell together); stamp duty = 0.00% on buys (0 = spread bet, the basis for all results from 26 Oct 2026, including earlier trades). Grey rows were never entered or have no result yet. Results rechecked with version 3 missing-price safeguards; older totals may differ. Only resolved trades enter the totals.</t>
+          <t>Each trade is £100. Dealing costs = 0.10% (buy and sell together); stamp duty = 0.00% on buys (0 = spread bet, the basis for all results from 26 Oct 2026, including earlier trades). Only completed trades are listed: skipped trades and those without a result yet are left out. Results rechecked with version 3 missing-price safeguards; older totals may differ. Only resolved trades enter the totals.</t>
         </is>
       </c>
     </row>
@@ -687,20 +686,15 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>Not resolved / skipped</t>
+          <t>Gross profit / loss (£)</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t>Gross profit / loss (£)</t>
+          <t>Dealing costs (£)</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t>Dealing costs (£)</t>
-        </is>
-      </c>
-      <c r="I4" s="3" t="inlineStr">
         <is>
           <t>Stamp duty (£)</t>
         </is>
@@ -722,16 +716,13 @@
       <c r="E5" s="1" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="1" t="n">
-        <v>5</v>
+      <c r="F5" s="4" t="n">
+        <v>1.83</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>1.83</v>
+        <v>-2.9</v>
       </c>
       <c r="H5" s="4" t="n">
-        <v>-2.9</v>
-      </c>
-      <c r="I5" s="4" t="n">
         <v>-0</v>
       </c>
     </row>
@@ -2974,247 +2965,6 @@
       </c>
       <c r="R41" s="11" t="n">
         <v>-1.07</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B42" s="12" t="inlineStr">
-        <is>
-          <t>08:32</t>
-        </is>
-      </c>
-      <c r="C42" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>Hammerson</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>HMSO.L</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>Long</t>
-        </is>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="n"/>
-      <c r="I42" s="12" t="n">
-        <v>346.55</v>
-      </c>
-      <c r="J42" s="12" t="n">
-        <v>352.35</v>
-      </c>
-      <c r="K42" s="12" t="inlineStr">
-        <is>
-          <t>Not resolved yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-22</t>
-        </is>
-      </c>
-      <c r="B43" s="12" t="inlineStr">
-        <is>
-          <t>08:47</t>
-        </is>
-      </c>
-      <c r="C43" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D43" s="12" t="inlineStr">
-        <is>
-          <t>ME Group International</t>
-        </is>
-      </c>
-      <c r="E43" s="12" t="inlineStr">
-        <is>
-          <t>MEGP.L</t>
-        </is>
-      </c>
-      <c r="F43" s="12" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="G43" s="12" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="H43" s="12" t="n"/>
-      <c r="I43" s="12" t="n">
-        <v>112.35</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>108.54</v>
-      </c>
-      <c r="K43" s="12" t="inlineStr">
-        <is>
-          <t>Not resolved yet</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-26</t>
-        </is>
-      </c>
-      <c r="B44" s="12" t="inlineStr">
-        <is>
-          <t>12:17</t>
-        </is>
-      </c>
-      <c r="C44" s="12" t="n">
-        <v>5</v>
-      </c>
-      <c r="D44" s="12" t="inlineStr">
-        <is>
-          <t>Severn Trent</t>
-        </is>
-      </c>
-      <c r="E44" s="12" t="inlineStr">
-        <is>
-          <t>SVT.L</t>
-        </is>
-      </c>
-      <c r="F44" s="12" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="G44" s="12" t="inlineStr">
-        <is>
-          <t>Breakout</t>
-        </is>
-      </c>
-      <c r="H44" s="12" t="n">
-        <v>3264</v>
-      </c>
-      <c r="I44" s="12" t="n">
-        <v>3263.99</v>
-      </c>
-      <c r="J44" s="12" t="n">
-        <v>3208.02</v>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>Skipped (price already past stop or target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B45" s="12" t="inlineStr">
-        <is>
-          <t>08:32</t>
-        </is>
-      </c>
-      <c r="C45" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>Whitbread</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>WTB.L</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="n">
-        <v>2583.22</v>
-      </c>
-      <c r="I45" s="12" t="n">
-        <v>2580.12</v>
-      </c>
-      <c r="J45" s="12" t="n">
-        <v>2555.62</v>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>Skipped (price already past stop or target)</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="12" t="inlineStr">
-        <is>
-          <t>2026-10-27</t>
-        </is>
-      </c>
-      <c r="B46" s="12" t="inlineStr">
-        <is>
-          <t>09:02</t>
-        </is>
-      </c>
-      <c r="C46" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>Hiscox</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>HSX.L</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>Short</t>
-        </is>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>Range</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="n">
-        <v>1839</v>
-      </c>
-      <c r="I46" s="12" t="n">
-        <v>1836.75</v>
-      </c>
-      <c r="J46" s="12" t="n">
-        <v>1821.75</v>
-      </c>
-      <c r="K46" s="12" t="inlineStr">
-        <is>
-          <t>Skipped (price already past stop or target)</t>
-        </is>
       </c>
     </row>
   </sheetData>

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -647,7 +647,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-27 21:29 UK time. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
+          <t>Generated 2026-10-27 21:41 UK time. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
         </is>
       </c>
     </row>

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -223,12 +223,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily'!$A$2:$A$7</f>
+              <f>'Daily'!$A$2:$A$8</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily'!$B$2:$B$7</f>
+              <f>'Daily'!$B$2:$B$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -614,7 +614,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R41"/>
+  <dimension ref="A1:R47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -647,7 +647,7 @@
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated 2026-10-27 21:41 UK time. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
+          <t>Generated 2026-10-28 17:07 UK time. The live mock trader enters ideas as they trigger during the day: every idea that passes the rules, up to 5 open at once and 10 a day (before 26 Oct 2026: 1 new trade per scan and 5 a day; before 23 Oct: 3 a day), one per share, FTSE 100 shares only from 23 Oct 2026, and only ideas that pass the entry rules, including the check that the target would pay more than the stop could cost after costs. Each entry was saved the moment the scan ran (scan_data/live_mock_trades.csv) and is filled at the open of the next 15-minute candle. Trades close at the target, the stop, or the end of the day.</t>
         </is>
       </c>
     </row>
@@ -702,25 +702,25 @@
     </row>
     <row r="5">
       <c r="A5" s="4" t="n">
-        <v>-1.07</v>
+        <v>-0.36</v>
       </c>
       <c r="B5" s="1" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="D5" s="1" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="E5" s="1" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="4" t="n">
-        <v>1.83</v>
+        <v>3.14</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>-2.9</v>
+        <v>-3.5</v>
       </c>
       <c r="H5" s="4" t="n">
         <v>-0</v>
@@ -765,19 +765,19 @@
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>-0.04</v>
+        <v>-0.01</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>862</v>
+        <v>991</v>
       </c>
       <c r="E8" s="6" t="n">
-        <v>-0.08</v>
+        <v>-0.1</v>
       </c>
       <c r="F8" s="6" t="n">
-        <v>0.05</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
@@ -2965,6 +2965,438 @@
       </c>
       <c r="R41" s="11" t="n">
         <v>-1.07</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="n">
+        <v>3</v>
+      </c>
+      <c r="D42" s="10" t="inlineStr">
+        <is>
+          <t>Computacenter</t>
+        </is>
+      </c>
+      <c r="E42" s="10" t="inlineStr">
+        <is>
+          <t>CCC.L</t>
+        </is>
+      </c>
+      <c r="F42" s="10" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G42" s="10" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="H42" s="10" t="n">
+        <v>5290</v>
+      </c>
+      <c r="I42" s="10" t="n">
+        <v>5223.73</v>
+      </c>
+      <c r="J42" s="10" t="n">
+        <v>5308.8</v>
+      </c>
+      <c r="K42" s="10" t="inlineStr">
+        <is>
+          <t>Target hit</t>
+        </is>
+      </c>
+      <c r="L42" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-28 10:30</t>
+        </is>
+      </c>
+      <c r="M42" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N42" s="11" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="O42" s="11" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P42" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="11" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="R42" s="11" t="n">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B43" s="10" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="C43" s="10" t="n">
+        <v>6</v>
+      </c>
+      <c r="D43" s="10" t="inlineStr">
+        <is>
+          <t>IMI</t>
+        </is>
+      </c>
+      <c r="E43" s="10" t="inlineStr">
+        <is>
+          <t>IMI.L</t>
+        </is>
+      </c>
+      <c r="F43" s="10" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G43" s="10" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="H43" s="10" t="n">
+        <v>2886</v>
+      </c>
+      <c r="I43" s="10" t="n">
+        <v>2864.36</v>
+      </c>
+      <c r="J43" s="10" t="n">
+        <v>2894.93</v>
+      </c>
+      <c r="K43" s="10" t="inlineStr">
+        <is>
+          <t>Target hit</t>
+        </is>
+      </c>
+      <c r="L43" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-28 11:00</t>
+        </is>
+      </c>
+      <c r="M43" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N43" s="11" t="n">
+        <v>0.31</v>
+      </c>
+      <c r="O43" s="11" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P43" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q43" s="11" t="n">
+        <v>0.21</v>
+      </c>
+      <c r="R43" s="11" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B44" s="8" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C44" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="D44" s="8" t="inlineStr">
+        <is>
+          <t>Croda International</t>
+        </is>
+      </c>
+      <c r="E44" s="8" t="inlineStr">
+        <is>
+          <t>CRDA.L</t>
+        </is>
+      </c>
+      <c r="F44" s="8" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G44" s="8" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="H44" s="8" t="n">
+        <v>3590</v>
+      </c>
+      <c r="I44" s="8" t="n">
+        <v>3620</v>
+      </c>
+      <c r="J44" s="8" t="n">
+        <v>3544</v>
+      </c>
+      <c r="K44" s="8" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L44" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-28 13:15</t>
+        </is>
+      </c>
+      <c r="M44" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N44" s="9" t="n">
+        <v>-0.84</v>
+      </c>
+      <c r="O44" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P44" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q44" s="9" t="n">
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="R44" s="9" t="n">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B45" s="8" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="C45" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="D45" s="8" t="inlineStr">
+        <is>
+          <t>Standard Life</t>
+        </is>
+      </c>
+      <c r="E45" s="8" t="inlineStr">
+        <is>
+          <t>SDLF.L</t>
+        </is>
+      </c>
+      <c r="F45" s="8" t="inlineStr">
+        <is>
+          <t>Long</t>
+        </is>
+      </c>
+      <c r="G45" s="8" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="H45" s="8" t="n">
+        <v>926.85</v>
+      </c>
+      <c r="I45" s="8" t="n">
+        <v>924.5</v>
+      </c>
+      <c r="J45" s="8" t="n">
+        <v>936.5</v>
+      </c>
+      <c r="K45" s="8" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L45" s="8" t="inlineStr">
+        <is>
+          <t>2026-10-28 14:30</t>
+        </is>
+      </c>
+      <c r="M45" s="9" t="n">
+        <v>100</v>
+      </c>
+      <c r="N45" s="9" t="n">
+        <v>-0.25</v>
+      </c>
+      <c r="O45" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P45" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q45" s="9" t="n">
+        <v>-0.35</v>
+      </c>
+      <c r="R45" s="9" t="n">
+        <v>-1.89</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C46" s="10" t="n">
+        <v>2</v>
+      </c>
+      <c r="D46" s="10" t="inlineStr">
+        <is>
+          <t>Marks &amp; Spencer</t>
+        </is>
+      </c>
+      <c r="E46" s="10" t="inlineStr">
+        <is>
+          <t>MKS.L</t>
+        </is>
+      </c>
+      <c r="F46" s="10" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G46" s="10" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="H46" s="10" t="n">
+        <v>412.5</v>
+      </c>
+      <c r="I46" s="10" t="n">
+        <v>415.37</v>
+      </c>
+      <c r="J46" s="10" t="n">
+        <v>404.15</v>
+      </c>
+      <c r="K46" s="10" t="inlineStr">
+        <is>
+          <t>Closed at end of day</t>
+        </is>
+      </c>
+      <c r="L46" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:30</t>
+        </is>
+      </c>
+      <c r="M46" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N46" s="11" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="O46" s="11" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P46" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q46" s="11" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="R46" s="11" t="n">
+        <v>-0.61</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C47" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="D47" s="10" t="inlineStr">
+        <is>
+          <t>Segro</t>
+        </is>
+      </c>
+      <c r="E47" s="10" t="inlineStr">
+        <is>
+          <t>SGRO.L</t>
+        </is>
+      </c>
+      <c r="F47" s="10" t="inlineStr">
+        <is>
+          <t>Short</t>
+        </is>
+      </c>
+      <c r="G47" s="10" t="inlineStr">
+        <is>
+          <t>Breakout</t>
+        </is>
+      </c>
+      <c r="H47" s="10" t="n">
+        <v>907.6</v>
+      </c>
+      <c r="I47" s="10" t="n">
+        <v>912.9</v>
+      </c>
+      <c r="J47" s="10" t="n">
+        <v>892.4299999999999</v>
+      </c>
+      <c r="K47" s="10" t="inlineStr">
+        <is>
+          <t>Closed at end of day</t>
+        </is>
+      </c>
+      <c r="L47" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-28 16:30</t>
+        </is>
+      </c>
+      <c r="M47" s="11" t="n">
+        <v>100</v>
+      </c>
+      <c r="N47" s="11" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="O47" s="11" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P47" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q47" s="11" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="R47" s="11" t="n">
+        <v>-0.36</v>
       </c>
     </row>
   </sheetData>
@@ -2983,7 +3415,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B10"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3062,10 +3494,20 @@
         <v>-1.07</v>
       </c>
     </row>
-    <row r="8"/>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>2026-10-28</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>-0.36</v>
+      </c>
+    </row>
     <row r="9"/>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
+    <row r="10"/>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
         <is>
           <t>Each trade is £100, after dealing costs and stamp duty.</t>
         </is>

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily'!$A$2:$A$8</f>
+              <f>'Daily'!$A$2:$A$9</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily'!$B$2:$B$8</f>
+              <f>'Daily'!$B$2:$B$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P39"/>
+  <dimension ref="A1:P48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -683,32 +683,32 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>-0.36</v>
+        <v>-0.73</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>35</v>
+        <v>44</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>23</v>
+        <v>29</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.01</v>
+        <v>-0.02</v>
       </c>
       <c r="G2" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.11</v>
       </c>
       <c r="H2" s="2" t="n">
         <v>0.09</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-28 20:31</t>
+          <t>2026-10-29 17:07</t>
         </is>
       </c>
     </row>
@@ -3102,6 +3102,600 @@
       </c>
       <c r="P39" s="9" t="n">
         <v>-0.36</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B40" s="7" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C40" s="7" t="inlineStr">
+        <is>
+          <t>Haleon</t>
+        </is>
+      </c>
+      <c r="D40" s="7" t="inlineStr">
+        <is>
+          <t>HLN.L</t>
+        </is>
+      </c>
+      <c r="E40" s="7" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="F40" s="7" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n">
+        <v>329.87</v>
+      </c>
+      <c r="H40" s="7" t="n">
+        <v>333.5</v>
+      </c>
+      <c r="I40" s="7" t="n">
+        <v>327.72</v>
+      </c>
+      <c r="J40" s="8" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="K40" s="7" t="inlineStr">
+        <is>
+          <t>Target hit</t>
+        </is>
+      </c>
+      <c r="L40" s="7" t="inlineStr">
+        <is>
+          <t>10-29 09:00</t>
+        </is>
+      </c>
+      <c r="M40" s="9" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="N40" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O40" s="9" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P40" s="9" t="n">
+        <v>0.19</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B41" s="4" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C41" s="4" t="inlineStr">
+        <is>
+          <t>Admiral Group</t>
+        </is>
+      </c>
+      <c r="D41" s="4" t="inlineStr">
+        <is>
+          <t>ADM.L</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F41" s="4" t="inlineStr">
+        <is>
+          <t>Reclaim</t>
+        </is>
+      </c>
+      <c r="G41" s="4" t="n">
+        <v>3790</v>
+      </c>
+      <c r="H41" s="4" t="n">
+        <v>3774</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>3877.61</v>
+      </c>
+      <c r="J41" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K41" s="4" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L41" s="4" t="inlineStr">
+        <is>
+          <t>10-29 10:00</t>
+        </is>
+      </c>
+      <c r="M41" s="6" t="n">
+        <v>-0.47</v>
+      </c>
+      <c r="N41" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O41" s="6" t="n">
+        <v>-0.57</v>
+      </c>
+      <c r="P41" s="6" t="n">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B42" s="4" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="C42" s="4" t="inlineStr">
+        <is>
+          <t>IG Group</t>
+        </is>
+      </c>
+      <c r="D42" s="4" t="inlineStr">
+        <is>
+          <t>IGG.L</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="F42" s="4" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="G42" s="4" t="n">
+        <v>974</v>
+      </c>
+      <c r="H42" s="4" t="n">
+        <v>976.25</v>
+      </c>
+      <c r="I42" s="4" t="n">
+        <v>961.25</v>
+      </c>
+      <c r="J42" s="5" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="K42" s="4" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L42" s="4" t="inlineStr">
+        <is>
+          <t>10-29 11:15</t>
+        </is>
+      </c>
+      <c r="M42" s="6" t="n">
+        <v>-0.23</v>
+      </c>
+      <c r="N42" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O42" s="6" t="n">
+        <v>-0.33</v>
+      </c>
+      <c r="P42" s="6" t="n">
+        <v>-0.71</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B43" s="4" t="inlineStr">
+        <is>
+          <t>12:02</t>
+        </is>
+      </c>
+      <c r="C43" s="4" t="inlineStr">
+        <is>
+          <t>ICG</t>
+        </is>
+      </c>
+      <c r="D43" s="4" t="inlineStr">
+        <is>
+          <t>ICG.L</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="F43" s="4" t="inlineStr">
+        <is>
+          <t>Reclaim</t>
+        </is>
+      </c>
+      <c r="G43" s="4" t="n">
+        <v>1830</v>
+      </c>
+      <c r="H43" s="4" t="n">
+        <v>1842.88</v>
+      </c>
+      <c r="I43" s="4" t="n">
+        <v>1795.38</v>
+      </c>
+      <c r="J43" s="5" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="K43" s="4" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L43" s="4" t="inlineStr">
+        <is>
+          <t>10-29 13:15</t>
+        </is>
+      </c>
+      <c r="M43" s="6" t="n">
+        <v>-0.7</v>
+      </c>
+      <c r="N43" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O43" s="6" t="n">
+        <v>-0.8</v>
+      </c>
+      <c r="P43" s="6" t="n">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B44" s="4" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C44" s="4" t="inlineStr">
+        <is>
+          <t>Bunzl</t>
+        </is>
+      </c>
+      <c r="D44" s="4" t="inlineStr">
+        <is>
+          <t>BNZL.L</t>
+        </is>
+      </c>
+      <c r="E44" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F44" s="4" t="inlineStr">
+        <is>
+          <t>Reclaim</t>
+        </is>
+      </c>
+      <c r="G44" s="4" t="n">
+        <v>2842</v>
+      </c>
+      <c r="H44" s="4" t="n">
+        <v>2830</v>
+      </c>
+      <c r="I44" s="4" t="n">
+        <v>2902</v>
+      </c>
+      <c r="J44" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="K44" s="4" t="inlineStr">
+        <is>
+          <t>End of day</t>
+        </is>
+      </c>
+      <c r="L44" s="4" t="inlineStr">
+        <is>
+          <t>10-29 16:30</t>
+        </is>
+      </c>
+      <c r="M44" s="6" t="n">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="N44" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O44" s="6" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="P44" s="6" t="n">
+        <v>-1.54</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B45" s="4" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C45" s="4" t="inlineStr">
+        <is>
+          <t>IHG Hotels &amp; Resorts</t>
+        </is>
+      </c>
+      <c r="D45" s="4" t="inlineStr">
+        <is>
+          <t>IHG.L</t>
+        </is>
+      </c>
+      <c r="E45" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F45" s="4" t="inlineStr">
+        <is>
+          <t>Reclaim</t>
+        </is>
+      </c>
+      <c r="G45" s="4" t="n">
+        <v>167.95</v>
+      </c>
+      <c r="H45" s="4" t="n">
+        <v>166.93</v>
+      </c>
+      <c r="I45" s="4" t="n">
+        <v>171.22</v>
+      </c>
+      <c r="J45" s="5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K45" s="4" t="inlineStr">
+        <is>
+          <t>End of day</t>
+        </is>
+      </c>
+      <c r="L45" s="4" t="inlineStr">
+        <is>
+          <t>10-29 16:30</t>
+        </is>
+      </c>
+      <c r="M45" s="6" t="n">
+        <v>-0.06</v>
+      </c>
+      <c r="N45" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O45" s="6" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="P45" s="6" t="n">
+        <v>-1.7</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B46" s="7" t="inlineStr">
+        <is>
+          <t>09:02</t>
+        </is>
+      </c>
+      <c r="C46" s="7" t="inlineStr">
+        <is>
+          <t>Associated British Foods</t>
+        </is>
+      </c>
+      <c r="D46" s="7" t="inlineStr">
+        <is>
+          <t>ABF.L</t>
+        </is>
+      </c>
+      <c r="E46" s="7" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="F46" s="7" t="inlineStr">
+        <is>
+          <t>Reclaim</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n">
+        <v>1899</v>
+      </c>
+      <c r="H46" s="7" t="n">
+        <v>1923</v>
+      </c>
+      <c r="I46" s="7" t="n">
+        <v>1880.47</v>
+      </c>
+      <c r="J46" s="8" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="K46" s="7" t="inlineStr">
+        <is>
+          <t>Target hit</t>
+        </is>
+      </c>
+      <c r="L46" s="7" t="inlineStr">
+        <is>
+          <t>10-29 16:30</t>
+        </is>
+      </c>
+      <c r="M46" s="9" t="n">
+        <v>0.98</v>
+      </c>
+      <c r="N46" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O46" s="9" t="n">
+        <v>0.88</v>
+      </c>
+      <c r="P46" s="9" t="n">
+        <v>-0.82</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B47" s="4" t="inlineStr">
+        <is>
+          <t>09:17</t>
+        </is>
+      </c>
+      <c r="C47" s="4" t="inlineStr">
+        <is>
+          <t>3i</t>
+        </is>
+      </c>
+      <c r="D47" s="4" t="inlineStr">
+        <is>
+          <t>III.L</t>
+        </is>
+      </c>
+      <c r="E47" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F47" s="4" t="inlineStr">
+        <is>
+          <t>Reclaim</t>
+        </is>
+      </c>
+      <c r="G47" s="4" t="n">
+        <v>2420</v>
+      </c>
+      <c r="H47" s="4" t="n">
+        <v>2393.57</v>
+      </c>
+      <c r="I47" s="4" t="n">
+        <v>2464.32</v>
+      </c>
+      <c r="J47" s="5" t="n">
+        <v>1.09</v>
+      </c>
+      <c r="K47" s="4" t="inlineStr">
+        <is>
+          <t>End of day</t>
+        </is>
+      </c>
+      <c r="L47" s="4" t="inlineStr">
+        <is>
+          <t>10-29 16:30</t>
+        </is>
+      </c>
+      <c r="M47" s="6" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="N47" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O47" s="6" t="n">
+        <v>-0.39</v>
+      </c>
+      <c r="P47" s="6" t="n">
+        <v>-1.21</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B48" s="7" t="inlineStr">
+        <is>
+          <t>13:16</t>
+        </is>
+      </c>
+      <c r="C48" s="7" t="inlineStr">
+        <is>
+          <t>Computacenter</t>
+        </is>
+      </c>
+      <c r="D48" s="7" t="inlineStr">
+        <is>
+          <t>CCC.L</t>
+        </is>
+      </c>
+      <c r="E48" s="7" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F48" s="7" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="G48" s="7" t="n">
+        <v>5200</v>
+      </c>
+      <c r="H48" s="7" t="n">
+        <v>5181.25</v>
+      </c>
+      <c r="I48" s="7" t="n">
+        <v>5276.25</v>
+      </c>
+      <c r="J48" s="8" t="n">
+        <v>0.36</v>
+      </c>
+      <c r="K48" s="7" t="inlineStr">
+        <is>
+          <t>End of day</t>
+        </is>
+      </c>
+      <c r="L48" s="7" t="inlineStr">
+        <is>
+          <t>10-29 16:30</t>
+        </is>
+      </c>
+      <c r="M48" s="9" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="N48" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O48" s="9" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="P48" s="9" t="n">
+        <v>-0.73</v>
       </c>
     </row>
   </sheetData>
@@ -3115,7 +3709,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B11"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3204,10 +3798,20 @@
         <v>-0.36</v>
       </c>
     </row>
-    <row r="9"/>
+    <row r="9">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-29</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>-0.73</v>
+      </c>
+    </row>
     <row r="10"/>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
+    <row r="11"/>
+    <row r="12">
+      <c r="A12" s="10" t="inlineStr">
         <is>
           <t>Each trade is £100, after dealing costs and stamp duty.</t>
         </is>
@@ -3252,7 +3856,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>Paper only, no real orders. Generated 2026-10-28 20:31 UK time.</t>
+          <t>Paper only, no real orders. Generated 2026-10-29 17:07 UK time.</t>
         </is>
       </c>
     </row>

--- a/ftse_outcomes.xlsx
+++ b/ftse_outcomes.xlsx
@@ -222,12 +222,12 @@
           </marker>
           <cat>
             <numRef>
-              <f>'Daily'!$A$2:$A$9</f>
+              <f>'Daily'!$A$2:$A$10</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Daily'!$B$2:$B$9</f>
+              <f>'Daily'!$B$2:$B$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -613,7 +613,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P48"/>
+  <dimension ref="A1:P56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -683,32 +683,32 @@
     </row>
     <row r="2">
       <c r="A2" s="2" t="n">
-        <v>-0.73</v>
+        <v>-4.04</v>
       </c>
       <c r="B2" s="3" t="n">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C2" s="3" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="D2" s="3" t="n">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="E2" s="3" t="n">
         <v>0</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.08</v>
       </c>
       <c r="G2" s="2" t="n">
         <v>-0.11</v>
       </c>
       <c r="H2" s="2" t="n">
-        <v>0.09</v>
+        <v>0.03</v>
       </c>
       <c r="I2" s="3" t="inlineStr">
         <is>
-          <t>2026-10-29 17:07</t>
+          <t>2026-10-30 17:07</t>
         </is>
       </c>
     </row>
@@ -3696,6 +3696,534 @@
       </c>
       <c r="P48" s="9" t="n">
         <v>-0.73</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B49" s="4" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C49" s="4" t="inlineStr">
+        <is>
+          <t>Autotrader Group</t>
+        </is>
+      </c>
+      <c r="D49" s="4" t="inlineStr">
+        <is>
+          <t>AUTO.L</t>
+        </is>
+      </c>
+      <c r="E49" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F49" s="4" t="inlineStr">
+        <is>
+          <t>Reclaim</t>
+        </is>
+      </c>
+      <c r="G49" s="4" t="n">
+        <v>539.2</v>
+      </c>
+      <c r="H49" s="4" t="n">
+        <v>535.33</v>
+      </c>
+      <c r="I49" s="4" t="n">
+        <v>549.22</v>
+      </c>
+      <c r="J49" s="5" t="n">
+        <v>0.72</v>
+      </c>
+      <c r="K49" s="4" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L49" s="4" t="inlineStr">
+        <is>
+          <t>10-30 09:15</t>
+        </is>
+      </c>
+      <c r="M49" s="6" t="n">
+        <v>-0.72</v>
+      </c>
+      <c r="N49" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O49" s="6" t="n">
+        <v>-0.82</v>
+      </c>
+      <c r="P49" s="6" t="n">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B50" s="4" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C50" s="4" t="inlineStr">
+        <is>
+          <t>Pearson plc</t>
+        </is>
+      </c>
+      <c r="D50" s="4" t="inlineStr">
+        <is>
+          <t>PSON.L</t>
+        </is>
+      </c>
+      <c r="E50" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F50" s="4" t="inlineStr">
+        <is>
+          <t>Reclaim</t>
+        </is>
+      </c>
+      <c r="G50" s="4" t="n">
+        <v>1319</v>
+      </c>
+      <c r="H50" s="4" t="n">
+        <v>1311.34</v>
+      </c>
+      <c r="I50" s="4" t="n">
+        <v>1349.97</v>
+      </c>
+      <c r="J50" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K50" s="4" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L50" s="4" t="inlineStr">
+        <is>
+          <t>10-30 10:00</t>
+        </is>
+      </c>
+      <c r="M50" s="6" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="N50" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O50" s="6" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="P50" s="6" t="n">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B51" s="4" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C51" s="4" t="inlineStr">
+        <is>
+          <t>Tritax Big Box REIT</t>
+        </is>
+      </c>
+      <c r="D51" s="4" t="inlineStr">
+        <is>
+          <t>BBOX.L</t>
+        </is>
+      </c>
+      <c r="E51" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F51" s="4" t="inlineStr">
+        <is>
+          <t>Reclaim</t>
+        </is>
+      </c>
+      <c r="G51" s="4" t="n">
+        <v>146.4</v>
+      </c>
+      <c r="H51" s="4" t="n">
+        <v>145.5</v>
+      </c>
+      <c r="I51" s="4" t="n">
+        <v>149.14</v>
+      </c>
+      <c r="J51" s="5" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="K51" s="4" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L51" s="4" t="inlineStr">
+        <is>
+          <t>10-30 10:15</t>
+        </is>
+      </c>
+      <c r="M51" s="6" t="n">
+        <v>-0.61</v>
+      </c>
+      <c r="N51" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O51" s="6" t="n">
+        <v>-0.71</v>
+      </c>
+      <c r="P51" s="6" t="n">
+        <v>-2.94</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B52" s="4" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="C52" s="4" t="inlineStr">
+        <is>
+          <t>Howdens Joinery</t>
+        </is>
+      </c>
+      <c r="D52" s="4" t="inlineStr">
+        <is>
+          <t>HWDN.L</t>
+        </is>
+      </c>
+      <c r="E52" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F52" s="4" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="G52" s="4" t="n">
+        <v>809.5</v>
+      </c>
+      <c r="H52" s="4" t="n">
+        <v>808</v>
+      </c>
+      <c r="I52" s="4" t="n">
+        <v>816</v>
+      </c>
+      <c r="J52" s="5" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="K52" s="4" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L52" s="4" t="inlineStr">
+        <is>
+          <t>10-30 14:00</t>
+        </is>
+      </c>
+      <c r="M52" s="6" t="n">
+        <v>-0.19</v>
+      </c>
+      <c r="N52" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O52" s="6" t="n">
+        <v>-0.29</v>
+      </c>
+      <c r="P52" s="6" t="n">
+        <v>-3.23</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B53" s="4" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C53" s="4" t="inlineStr">
+        <is>
+          <t>Bunzl</t>
+        </is>
+      </c>
+      <c r="D53" s="4" t="inlineStr">
+        <is>
+          <t>BNZL.L</t>
+        </is>
+      </c>
+      <c r="E53" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F53" s="4" t="inlineStr">
+        <is>
+          <t>Reclaim</t>
+        </is>
+      </c>
+      <c r="G53" s="4" t="n">
+        <v>2880</v>
+      </c>
+      <c r="H53" s="4" t="n">
+        <v>2863.25</v>
+      </c>
+      <c r="I53" s="4" t="n">
+        <v>2922.25</v>
+      </c>
+      <c r="J53" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K53" s="4" t="inlineStr">
+        <is>
+          <t>Stopped out</t>
+        </is>
+      </c>
+      <c r="L53" s="4" t="inlineStr">
+        <is>
+          <t>10-30 16:15</t>
+        </is>
+      </c>
+      <c r="M53" s="6" t="n">
+        <v>-0.58</v>
+      </c>
+      <c r="N53" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O53" s="6" t="n">
+        <v>-0.68</v>
+      </c>
+      <c r="P53" s="6" t="n">
+        <v>-3.91</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B54" s="4" t="inlineStr">
+        <is>
+          <t>08:32</t>
+        </is>
+      </c>
+      <c r="C54" s="4" t="inlineStr">
+        <is>
+          <t>Rentokil Initial</t>
+        </is>
+      </c>
+      <c r="D54" s="4" t="inlineStr">
+        <is>
+          <t>RTO.L</t>
+        </is>
+      </c>
+      <c r="E54" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F54" s="4" t="inlineStr">
+        <is>
+          <t>Reclaim</t>
+        </is>
+      </c>
+      <c r="G54" s="4" t="n">
+        <v>351.1</v>
+      </c>
+      <c r="H54" s="4" t="n">
+        <v>349.54</v>
+      </c>
+      <c r="I54" s="4" t="n">
+        <v>358.25</v>
+      </c>
+      <c r="J54" s="5" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="K54" s="4" t="inlineStr">
+        <is>
+          <t>End of day</t>
+        </is>
+      </c>
+      <c r="L54" s="4" t="inlineStr">
+        <is>
+          <t>10-30 16:30</t>
+        </is>
+      </c>
+      <c r="M54" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O54" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="P54" s="6" t="n">
+        <v>-4.01</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="7" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B55" s="7" t="inlineStr">
+        <is>
+          <t>09:32</t>
+        </is>
+      </c>
+      <c r="C55" s="7" t="inlineStr">
+        <is>
+          <t>Spirax Group</t>
+        </is>
+      </c>
+      <c r="D55" s="7" t="inlineStr">
+        <is>
+          <t>SPX.L</t>
+        </is>
+      </c>
+      <c r="E55" s="7" t="inlineStr">
+        <is>
+          <t>Sell</t>
+        </is>
+      </c>
+      <c r="F55" s="7" t="inlineStr">
+        <is>
+          <t>Range</t>
+        </is>
+      </c>
+      <c r="G55" s="7" t="n">
+        <v>7530</v>
+      </c>
+      <c r="H55" s="7" t="n">
+        <v>7581.25</v>
+      </c>
+      <c r="I55" s="7" t="n">
+        <v>7456.25</v>
+      </c>
+      <c r="J55" s="8" t="n">
+        <v>0.68</v>
+      </c>
+      <c r="K55" s="7" t="inlineStr">
+        <is>
+          <t>End of day</t>
+        </is>
+      </c>
+      <c r="L55" s="7" t="inlineStr">
+        <is>
+          <t>10-30 16:30</t>
+        </is>
+      </c>
+      <c r="M55" s="9" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="N55" s="9" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O55" s="9" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="P55" s="9" t="n">
+        <v>-3.78</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="4" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B56" s="4" t="inlineStr">
+        <is>
+          <t>10:32</t>
+        </is>
+      </c>
+      <c r="C56" s="4" t="inlineStr">
+        <is>
+          <t>Coca-Cola HBC</t>
+        </is>
+      </c>
+      <c r="D56" s="4" t="inlineStr">
+        <is>
+          <t>CCH.L</t>
+        </is>
+      </c>
+      <c r="E56" s="4" t="inlineStr">
+        <is>
+          <t>Buy</t>
+        </is>
+      </c>
+      <c r="F56" s="4" t="inlineStr">
+        <is>
+          <t>Reclaim</t>
+        </is>
+      </c>
+      <c r="G56" s="4" t="n">
+        <v>4701.36</v>
+      </c>
+      <c r="H56" s="4" t="n">
+        <v>4673.9</v>
+      </c>
+      <c r="I56" s="4" t="n">
+        <v>4762.31</v>
+      </c>
+      <c r="J56" s="5" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="K56" s="4" t="inlineStr">
+        <is>
+          <t>End of day</t>
+        </is>
+      </c>
+      <c r="L56" s="4" t="inlineStr">
+        <is>
+          <t>10-30 16:30</t>
+        </is>
+      </c>
+      <c r="M56" s="6" t="n">
+        <v>-0.16</v>
+      </c>
+      <c r="N56" s="6" t="n">
+        <v>-0.1</v>
+      </c>
+      <c r="O56" s="6" t="n">
+        <v>-0.26</v>
+      </c>
+      <c r="P56" s="6" t="n">
+        <v>-4.04</v>
       </c>
     </row>
   </sheetData>
@@ -3709,7 +4237,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3808,10 +4336,20 @@
         <v>-0.73</v>
       </c>
     </row>
-    <row r="10"/>
+    <row r="10">
+      <c r="A10" s="10" t="inlineStr">
+        <is>
+          <t>2026-10-30</t>
+        </is>
+      </c>
+      <c r="B10" s="11" t="n">
+        <v>-4.04</v>
+      </c>
+    </row>
     <row r="11"/>
-    <row r="12">
-      <c r="A12" s="10" t="inlineStr">
+    <row r="12"/>
+    <row r="13">
+      <c r="A13" s="10" t="inlineStr">
         <is>
           <t>Each trade is £100, after dealing costs and stamp duty.</t>
         </is>
@@ -3856,7 +4394,7 @@
       </c>
       <c r="B2" s="13" t="inlineStr">
         <is>
-          <t>Paper only, no real orders. Generated 2026-10-29 17:07 UK time.</t>
+          <t>Paper only, no real orders. Generated 2026-10-30 17:07 UK time.</t>
         </is>
       </c>
     </row>
